--- a/research/traditional_assets/database/data/poland/poland_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_r_e_i_t.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="wse_hrl" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,28 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.723</v>
-      </c>
-      <c r="E2">
-        <v>0.255</v>
+        <v>1.86</v>
       </c>
       <c r="G2">
-        <v>-0.3736842105263158</v>
+        <v>-2.367875647668394</v>
       </c>
       <c r="H2">
-        <v>-0.3736842105263158</v>
+        <v>-2.367875647668394</v>
       </c>
       <c r="I2">
-        <v>-0.5964912280701755</v>
+        <v>0.06217616580310881</v>
       </c>
       <c r="J2">
-        <v>-0.5964912280701755</v>
+        <v>0.06217616580310881</v>
       </c>
       <c r="K2">
-        <v>0.222</v>
+        <v>-0.195</v>
       </c>
       <c r="L2">
-        <v>0.1947368421052632</v>
+        <v>-1.010362694300518</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,67 +638,67 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.06416184971098265</v>
+        <v>-0.07303370786516854</v>
       </c>
       <c r="X2">
-        <v>0.07329326280621305</v>
+        <v>0.1162517821552733</v>
       </c>
       <c r="Y2">
-        <v>-0.009131413095230398</v>
+        <v>-0.1892854900204418</v>
       </c>
       <c r="Z2">
-        <v>0.1572413793103448</v>
+        <v>0.03282312925170068</v>
       </c>
       <c r="AA2">
-        <v>-0.09379310344827586</v>
+        <v>0.002040816326530612</v>
       </c>
       <c r="AB2">
-        <v>0.05585046897959708</v>
+        <v>0.0805331540049174</v>
       </c>
       <c r="AC2">
-        <v>-0.1496435724278729</v>
+        <v>-0.07849233767838679</v>
       </c>
       <c r="AD2">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="AG2">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="AH2">
-        <v>0.4120667522464698</v>
+        <v>0.5641421947449768</v>
       </c>
       <c r="AI2">
-        <v>0.5459183673469388</v>
+        <v>0.7087378640776698</v>
       </c>
       <c r="AJ2">
-        <v>0.4120667522464698</v>
+        <v>0.5641421947449768</v>
       </c>
       <c r="AK2">
-        <v>0.5459183673469388</v>
+        <v>0.7087378640776698</v>
       </c>
       <c r="AL2">
-        <v>0.236</v>
+        <v>0.202</v>
       </c>
       <c r="AM2">
-        <v>0.213</v>
+        <v>0.202</v>
       </c>
       <c r="AN2">
-        <v>-4.776785714285714</v>
+        <v>34.11214953271028</v>
       </c>
       <c r="AO2">
-        <v>-2.88135593220339</v>
+        <v>0.0594059405940594</v>
       </c>
       <c r="AP2">
-        <v>-4.776785714285714</v>
+        <v>34.11214953271028</v>
       </c>
       <c r="AQ2">
-        <v>-3.192488262910798</v>
+        <v>0.0594059405940594</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.723</v>
-      </c>
-      <c r="E3">
-        <v>0.255</v>
+        <v>1.86</v>
       </c>
       <c r="G3">
-        <v>-0.3736842105263158</v>
+        <v>-2.367875647668394</v>
       </c>
       <c r="H3">
-        <v>-0.3736842105263158</v>
+        <v>-2.367875647668394</v>
       </c>
       <c r="I3">
-        <v>-0.5964912280701755</v>
+        <v>0.06217616580310881</v>
       </c>
       <c r="J3">
-        <v>-0.5964912280701755</v>
+        <v>0.06217616580310881</v>
       </c>
       <c r="K3">
-        <v>0.222</v>
+        <v>-0.195</v>
       </c>
       <c r="L3">
-        <v>0.1947368421052632</v>
+        <v>-1.010362694300518</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,7 +754,7 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,67 +766,8779 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.06416184971098265</v>
+        <v>-0.07303370786516854</v>
       </c>
       <c r="X3">
-        <v>0.07329326280621305</v>
+        <v>0.1162517821552733</v>
       </c>
       <c r="Y3">
-        <v>-0.009131413095230398</v>
+        <v>-0.1892854900204418</v>
       </c>
       <c r="Z3">
-        <v>0.1572413793103448</v>
+        <v>0.03282312925170068</v>
       </c>
       <c r="AA3">
-        <v>-0.09379310344827586</v>
+        <v>0.002040816326530612</v>
       </c>
       <c r="AB3">
-        <v>0.05585046897959708</v>
+        <v>0.0805331540049174</v>
       </c>
       <c r="AC3">
-        <v>-0.1496435724278729</v>
+        <v>-0.07849233767838679</v>
       </c>
       <c r="AD3">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="AG3">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="AH3">
-        <v>0.4120667522464698</v>
+        <v>0.5641421947449768</v>
       </c>
       <c r="AI3">
-        <v>0.5459183673469388</v>
+        <v>0.7087378640776698</v>
       </c>
       <c r="AJ3">
-        <v>0.4120667522464698</v>
+        <v>0.5641421947449768</v>
       </c>
       <c r="AK3">
-        <v>0.5459183673469388</v>
+        <v>0.7087378640776698</v>
       </c>
       <c r="AL3">
-        <v>0.236</v>
+        <v>0.202</v>
       </c>
       <c r="AM3">
-        <v>0.213</v>
+        <v>0.202</v>
       </c>
       <c r="AN3">
-        <v>-4.776785714285714</v>
+        <v>34.11214953271028</v>
       </c>
       <c r="AO3">
-        <v>-2.88135593220339</v>
+        <v>0.0594059405940594</v>
       </c>
       <c r="AP3">
-        <v>-4.776785714285714</v>
+        <v>34.11214953271028</v>
       </c>
       <c r="AQ3">
-        <v>-3.192488262910798</v>
+        <v>0.0594059405940594</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hornigold Reit S.A. (WSE:HRL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WSE:HRL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>R.E.I.T.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.564142194744977</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2.82</v>
+      </c>
+      <c r="H2">
+        <v>7.14117609868258</v>
+      </c>
+      <c r="I2">
+        <v>6.47</v>
+      </c>
+      <c r="J2">
+        <v>7.14117609868258</v>
+      </c>
+      <c r="K2">
+        <v>3.65</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.0805331540049174</v>
+      </c>
+      <c r="N2">
+        <v>0.07661078952269899</v>
+      </c>
+      <c r="O2">
+        <v>0.0529368440366973</v>
+      </c>
+      <c r="P2">
+        <v>0.037017</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.116251782155273</v>
+      </c>
+      <c r="T2">
+        <v>0.07661078952269899</v>
+      </c>
+      <c r="U2">
+        <v>1.05021941141932</v>
+      </c>
+      <c r="V2">
+        <v>0.512701244733399</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>2.82</v>
+      </c>
+      <c r="AB2">
+        <v>0.07374819139040771</v>
+      </c>
+      <c r="AC2">
+        <v>0.06535412844036698</v>
+      </c>
+      <c r="AD2">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.107</v>
+      </c>
+      <c r="AH2">
+        <v>0.094</v>
+      </c>
+      <c r="AI2">
+        <v>0.01100000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>3.65</v>
+      </c>
+      <c r="AK2">
+        <v>3.65</v>
+      </c>
+      <c r="AL2">
+        <v>0.202</v>
+      </c>
+      <c r="AM2">
+        <v>3.65</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.07661078952269895</v>
+      </c>
+      <c r="C2">
+        <v>7.141176098682582</v>
+      </c>
+      <c r="D2">
+        <v>7.141176098682582</v>
+      </c>
+      <c r="E2">
+        <v>-3.65</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>2.82</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.107</v>
+      </c>
+      <c r="K2">
+        <v>0.094</v>
+      </c>
+      <c r="L2">
+        <v>0.013</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.013</v>
+      </c>
+      <c r="O2">
+        <v>0.002469999999999999</v>
+      </c>
+      <c r="P2">
+        <v>0.01053</v>
+      </c>
+      <c r="Q2">
+        <v>0.10453</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.07661078952269895</v>
+      </c>
+      <c r="T2">
+        <v>0.5127012447333988</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.03701700000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.07689128902260585</v>
+      </c>
+      <c r="C3">
+        <v>7.02388936885995</v>
+      </c>
+      <c r="D3">
+        <v>7.08858936885995</v>
+      </c>
+      <c r="E3">
+        <v>-3.5853</v>
+      </c>
+      <c r="F3">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>2.82</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.107</v>
+      </c>
+      <c r="K3">
+        <v>0.094</v>
+      </c>
+      <c r="L3">
+        <v>0.013</v>
+      </c>
+      <c r="M3">
+        <v>0.00591358</v>
+      </c>
+      <c r="N3">
+        <v>0.007086419999999998</v>
+      </c>
+      <c r="O3">
+        <v>0.001346419799999999</v>
+      </c>
+      <c r="P3">
+        <v>0.005740000199999999</v>
+      </c>
+      <c r="Q3">
+        <v>0.0997400002</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.07692015052788469</v>
+      </c>
+      <c r="T3">
+        <v>0.5168960730993994</v>
+      </c>
+      <c r="U3">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V3">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.07403400000000002</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>2.198329945650519</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08016858063557848</v>
+      </c>
+      <c r="C4">
+        <v>6.397618869474919</v>
+      </c>
+      <c r="D4">
+        <v>6.52701886947492</v>
+      </c>
+      <c r="E4">
+        <v>-3.5206</v>
+      </c>
+      <c r="F4">
+        <v>0.1294</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>2.82</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.107</v>
+      </c>
+      <c r="K4">
+        <v>0.094</v>
+      </c>
+      <c r="L4">
+        <v>0.013</v>
+      </c>
+      <c r="M4">
+        <v>0.03090072</v>
+      </c>
+      <c r="N4">
+        <v>-0.01790072</v>
+      </c>
+      <c r="O4">
+        <v>-0.003401136799999999</v>
+      </c>
+      <c r="P4">
+        <v>-0.0144995832</v>
+      </c>
+      <c r="Q4">
+        <v>0.0795004168</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.07732075776932669</v>
+      </c>
+      <c r="T4">
+        <v>0.5223281689093329</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>0.07993341255478834</v>
+      </c>
+      <c r="W4">
+        <v>0.2197119010819165</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>0.4207021713409913</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08216858063557848</v>
+      </c>
+      <c r="C5">
+        <v>6.031916679695146</v>
+      </c>
+      <c r="D5">
+        <v>6.226016679695146</v>
+      </c>
+      <c r="E5">
+        <v>-3.4559</v>
+      </c>
+      <c r="F5">
+        <v>0.1941</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>2.82</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.107</v>
+      </c>
+      <c r="K5">
+        <v>0.094</v>
+      </c>
+      <c r="L5">
+        <v>0.013</v>
+      </c>
+      <c r="M5">
+        <v>0.04635108</v>
+      </c>
+      <c r="N5">
+        <v>-0.03335108000000001</v>
+      </c>
+      <c r="O5">
+        <v>-0.006336705199999999</v>
+      </c>
+      <c r="P5">
+        <v>-0.0270143748</v>
+      </c>
+      <c r="Q5">
+        <v>0.0669856252</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.07771787898344347</v>
+      </c>
+      <c r="T5">
+        <v>0.5277129953929344</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>0.05328894170319222</v>
+      </c>
+      <c r="W5">
+        <v>0.2260746007212777</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>0.2804681142273275</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08416858063557849</v>
+      </c>
+      <c r="C6">
+        <v>5.692752872695962</v>
+      </c>
+      <c r="D6">
+        <v>5.951552872695962</v>
+      </c>
+      <c r="E6">
+        <v>-3.3912</v>
+      </c>
+      <c r="F6">
+        <v>0.2588</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>2.82</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.107</v>
+      </c>
+      <c r="K6">
+        <v>0.094</v>
+      </c>
+      <c r="L6">
+        <v>0.013</v>
+      </c>
+      <c r="M6">
+        <v>0.06180144</v>
+      </c>
+      <c r="N6">
+        <v>-0.04880144</v>
+      </c>
+      <c r="O6">
+        <v>-0.009272273599999997</v>
+      </c>
+      <c r="P6">
+        <v>-0.0395291664</v>
+      </c>
+      <c r="Q6">
+        <v>0.0544708336</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.07812327355618767</v>
+      </c>
+      <c r="T6">
+        <v>0.5332100057616107</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>0.03996670627739417</v>
+      </c>
+      <c r="W6">
+        <v>0.2292559505409583</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>0.2103510856704957</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08616858063557849</v>
+      </c>
+      <c r="C7">
+        <v>5.37676593131669</v>
+      </c>
+      <c r="D7">
+        <v>5.70026593131669</v>
+      </c>
+      <c r="E7">
+        <v>-3.3265</v>
+      </c>
+      <c r="F7">
+        <v>0.3235</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>2.82</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.107</v>
+      </c>
+      <c r="K7">
+        <v>0.094</v>
+      </c>
+      <c r="L7">
+        <v>0.013</v>
+      </c>
+      <c r="M7">
+        <v>0.07725180000000001</v>
+      </c>
+      <c r="N7">
+        <v>-0.06425180000000001</v>
+      </c>
+      <c r="O7">
+        <v>-0.012207842</v>
+      </c>
+      <c r="P7">
+        <v>-0.05204395800000002</v>
+      </c>
+      <c r="Q7">
+        <v>0.04195604199999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.07853720275151596</v>
+      </c>
+      <c r="T7">
+        <v>0.5388227426643645</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>0.03197336502191533</v>
+      </c>
+      <c r="W7">
+        <v>0.2311647604327667</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>0.1682808685363966</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08816858063557849</v>
+      </c>
+      <c r="C8">
+        <v>5.081139060098979</v>
+      </c>
+      <c r="D8">
+        <v>5.46933906009898</v>
+      </c>
+      <c r="E8">
+        <v>-3.2618</v>
+      </c>
+      <c r="F8">
+        <v>0.3882</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>2.82</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.107</v>
+      </c>
+      <c r="K8">
+        <v>0.094</v>
+      </c>
+      <c r="L8">
+        <v>0.013</v>
+      </c>
+      <c r="M8">
+        <v>0.09270216000000001</v>
+      </c>
+      <c r="N8">
+        <v>-0.07970216000000001</v>
+      </c>
+      <c r="O8">
+        <v>-0.0151434104</v>
+      </c>
+      <c r="P8">
+        <v>-0.06455874960000001</v>
+      </c>
+      <c r="Q8">
+        <v>0.02944125039999999</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.07895993895100017</v>
+      </c>
+      <c r="T8">
+        <v>0.5445548995012195</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>0.02664447085159611</v>
+      </c>
+      <c r="W8">
+        <v>0.2324373003606388</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.1402340571136638</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09016858063557849</v>
+      </c>
+      <c r="C9">
+        <v>4.80349414348157</v>
+      </c>
+      <c r="D9">
+        <v>5.25639414348157</v>
+      </c>
+      <c r="E9">
+        <v>-3.1971</v>
+      </c>
+      <c r="F9">
+        <v>0.4529</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>2.82</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.107</v>
+      </c>
+      <c r="K9">
+        <v>0.094</v>
+      </c>
+      <c r="L9">
+        <v>0.013</v>
+      </c>
+      <c r="M9">
+        <v>0.10815252</v>
+      </c>
+      <c r="N9">
+        <v>-0.09515252000000002</v>
+      </c>
+      <c r="O9">
+        <v>-0.0180789788</v>
+      </c>
+      <c r="P9">
+        <v>-0.07707354120000001</v>
+      </c>
+      <c r="Q9">
+        <v>0.01692645879999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.07939176625154856</v>
+      </c>
+      <c r="T9">
+        <v>0.5504103285281143</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>0.02283811787279666</v>
+      </c>
+      <c r="W9">
+        <v>0.2333462574519762</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.1202006203831404</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09216858063557851</v>
+      </c>
+      <c r="C10">
+        <v>4.541809547643268</v>
+      </c>
+      <c r="D10">
+        <v>5.059409547643268</v>
+      </c>
+      <c r="E10">
+        <v>-3.1324</v>
+      </c>
+      <c r="F10">
+        <v>0.5175999999999999</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>2.82</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.107</v>
+      </c>
+      <c r="K10">
+        <v>0.094</v>
+      </c>
+      <c r="L10">
+        <v>0.013</v>
+      </c>
+      <c r="M10">
+        <v>0.12360288</v>
+      </c>
+      <c r="N10">
+        <v>-0.11060288</v>
+      </c>
+      <c r="O10">
+        <v>-0.02101454719999999</v>
+      </c>
+      <c r="P10">
+        <v>-0.0895883328</v>
+      </c>
+      <c r="Q10">
+        <v>0.004411667199999997</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.07983298110210887</v>
+      </c>
+      <c r="T10">
+        <v>0.5563930494903764</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>0.01998335313869708</v>
+      </c>
+      <c r="W10">
+        <v>0.2340279752704792</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.1051755428352479</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09416858063557851</v>
+      </c>
+      <c r="C11">
+        <v>4.294355737104293</v>
+      </c>
+      <c r="D11">
+        <v>4.876655737104293</v>
+      </c>
+      <c r="E11">
+        <v>-3.0677</v>
+      </c>
+      <c r="F11">
+        <v>0.5822999999999999</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>2.82</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.107</v>
+      </c>
+      <c r="K11">
+        <v>0.094</v>
+      </c>
+      <c r="L11">
+        <v>0.013</v>
+      </c>
+      <c r="M11">
+        <v>0.13905324</v>
+      </c>
+      <c r="N11">
+        <v>-0.12605324</v>
+      </c>
+      <c r="O11">
+        <v>-0.0239501156</v>
+      </c>
+      <c r="P11">
+        <v>-0.1021031244</v>
+      </c>
+      <c r="Q11">
+        <v>-0.008103124400000022</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08028389298235183</v>
+      </c>
+      <c r="T11">
+        <v>0.5625072588254355</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>0.01776298056773074</v>
+      </c>
+      <c r="W11">
+        <v>0.2345582002404259</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.09348937140910907</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.0961685806355785</v>
+      </c>
+      <c r="C12">
+        <v>4.059644358643243</v>
+      </c>
+      <c r="D12">
+        <v>4.706644358643243</v>
+      </c>
+      <c r="E12">
+        <v>-3.003</v>
+      </c>
+      <c r="F12">
+        <v>0.647</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>2.82</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.107</v>
+      </c>
+      <c r="K12">
+        <v>0.094</v>
+      </c>
+      <c r="L12">
+        <v>0.013</v>
+      </c>
+      <c r="M12">
+        <v>0.1545036</v>
+      </c>
+      <c r="N12">
+        <v>-0.1415036</v>
+      </c>
+      <c r="O12">
+        <v>-0.02688568399999999</v>
+      </c>
+      <c r="P12">
+        <v>-0.114617916</v>
+      </c>
+      <c r="Q12">
+        <v>-0.02061791600000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08074482512660018</v>
+      </c>
+      <c r="T12">
+        <v>0.5687573394790515</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0.01598668251095766</v>
+      </c>
+      <c r="W12">
+        <v>0.2349823802163833</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.08414043426819839</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.0981685806355785</v>
+      </c>
+      <c r="C13">
+        <v>3.836387616735129</v>
+      </c>
+      <c r="D13">
+        <v>4.548087616735129</v>
+      </c>
+      <c r="E13">
+        <v>-2.9383</v>
+      </c>
+      <c r="F13">
+        <v>0.7117</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>2.82</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.107</v>
+      </c>
+      <c r="K13">
+        <v>0.094</v>
+      </c>
+      <c r="L13">
+        <v>0.013</v>
+      </c>
+      <c r="M13">
+        <v>0.16995396</v>
+      </c>
+      <c r="N13">
+        <v>-0.15695396</v>
+      </c>
+      <c r="O13">
+        <v>-0.02982125239999999</v>
+      </c>
+      <c r="P13">
+        <v>-0.1271327076</v>
+      </c>
+      <c r="Q13">
+        <v>-0.03313270760000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08121611529656197</v>
+      </c>
+      <c r="T13">
+        <v>0.5751478713833105</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0.01453334773723424</v>
+      </c>
+      <c r="W13">
+        <v>0.2353294365603485</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.07649130388018033</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1001685806355785</v>
+      </c>
+      <c r="C14">
+        <v>3.623465592708119</v>
+      </c>
+      <c r="D14">
+        <v>4.399865592708119</v>
+      </c>
+      <c r="E14">
+        <v>-2.8736</v>
+      </c>
+      <c r="F14">
+        <v>0.7764</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>2.82</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.107</v>
+      </c>
+      <c r="K14">
+        <v>0.094</v>
+      </c>
+      <c r="L14">
+        <v>0.013</v>
+      </c>
+      <c r="M14">
+        <v>0.18540432</v>
+      </c>
+      <c r="N14">
+        <v>-0.17240432</v>
+      </c>
+      <c r="O14">
+        <v>-0.03275682079999999</v>
+      </c>
+      <c r="P14">
+        <v>-0.1396474992</v>
+      </c>
+      <c r="Q14">
+        <v>-0.04564749920000002</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08169811660675018</v>
+      </c>
+      <c r="T14">
+        <v>0.5816836426490298</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.01332223542579805</v>
+      </c>
+      <c r="W14">
+        <v>0.2356186501803194</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.070117028556832</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1021685806355785</v>
+      </c>
+      <c r="C15">
+        <v>3.419899752615819</v>
+      </c>
+      <c r="D15">
+        <v>4.260999752615819</v>
+      </c>
+      <c r="E15">
+        <v>-2.8089</v>
+      </c>
+      <c r="F15">
+        <v>0.8411</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>2.82</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.107</v>
+      </c>
+      <c r="K15">
+        <v>0.094</v>
+      </c>
+      <c r="L15">
+        <v>0.013</v>
+      </c>
+      <c r="M15">
+        <v>0.20085468</v>
+      </c>
+      <c r="N15">
+        <v>-0.18785468</v>
+      </c>
+      <c r="O15">
+        <v>-0.03569238919999999</v>
+      </c>
+      <c r="P15">
+        <v>-0.1521622908</v>
+      </c>
+      <c r="Q15">
+        <v>-0.05816229080000002</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08219119840682777</v>
+      </c>
+      <c r="T15">
+        <v>0.5883696615300532</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.01229744808535205</v>
+      </c>
+      <c r="W15">
+        <v>0.2358633693972179</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.06472341097553724</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1041685806355785</v>
+      </c>
+      <c r="C16">
+        <v>3.224831318386832</v>
+      </c>
+      <c r="D16">
+        <v>4.130631318386833</v>
+      </c>
+      <c r="E16">
+        <v>-2.7442</v>
+      </c>
+      <c r="F16">
+        <v>0.9058</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>2.82</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.107</v>
+      </c>
+      <c r="K16">
+        <v>0.094</v>
+      </c>
+      <c r="L16">
+        <v>0.013</v>
+      </c>
+      <c r="M16">
+        <v>0.21630504</v>
+      </c>
+      <c r="N16">
+        <v>-0.20330504</v>
+      </c>
+      <c r="O16">
+        <v>-0.0386279576</v>
+      </c>
+      <c r="P16">
+        <v>-0.1646770824000001</v>
+      </c>
+      <c r="Q16">
+        <v>-0.07067708240000006</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08269574722551182</v>
+      </c>
+      <c r="T16">
+        <v>0.5952111692222631</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.01141905893639833</v>
+      </c>
+      <c r="W16">
+        <v>0.2360731287259881</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.06010031019157014</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1061685806355785</v>
+      </c>
+      <c r="C17">
+        <v>3.037503491604169</v>
+      </c>
+      <c r="D17">
+        <v>4.008003491604168</v>
+      </c>
+      <c r="E17">
+        <v>-2.6795</v>
+      </c>
+      <c r="F17">
+        <v>0.9704999999999999</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>2.82</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.107</v>
+      </c>
+      <c r="K17">
+        <v>0.094</v>
+      </c>
+      <c r="L17">
+        <v>0.013</v>
+      </c>
+      <c r="M17">
+        <v>0.2317554</v>
+      </c>
+      <c r="N17">
+        <v>-0.2187554</v>
+      </c>
+      <c r="O17">
+        <v>-0.04156352599999999</v>
+      </c>
+      <c r="P17">
+        <v>-0.177191874</v>
+      </c>
+      <c r="Q17">
+        <v>-0.083191874</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08321216778110607</v>
+      </c>
+      <c r="T17">
+        <v>0.6022136535660545</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.01065778834063844</v>
+      </c>
+      <c r="W17">
+        <v>0.2362549201442556</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.0560936228454656</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1081685806355785</v>
+      </c>
+      <c r="C18">
+        <v>2.857246752374924</v>
+      </c>
+      <c r="D18">
+        <v>3.892446752374924</v>
+      </c>
+      <c r="E18">
+        <v>-2.6148</v>
+      </c>
+      <c r="F18">
+        <v>1.0352</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>2.82</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.107</v>
+      </c>
+      <c r="K18">
+        <v>0.094</v>
+      </c>
+      <c r="L18">
+        <v>0.013</v>
+      </c>
+      <c r="M18">
+        <v>0.24720576</v>
+      </c>
+      <c r="N18">
+        <v>-0.23420576</v>
+      </c>
+      <c r="O18">
+        <v>-0.04449909439999999</v>
+      </c>
+      <c r="P18">
+        <v>-0.1897066656</v>
+      </c>
+      <c r="Q18">
+        <v>-0.09570666559999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08374088406421448</v>
+      </c>
+      <c r="T18">
+        <v>0.6093828637275551</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.009991676569348542</v>
+      </c>
+      <c r="W18">
+        <v>0.2364139876352396</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.05258777141762394</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1101685806355785</v>
+      </c>
+      <c r="C19">
+        <v>2.683466630065906</v>
+      </c>
+      <c r="D19">
+        <v>3.783366630065907</v>
+      </c>
+      <c r="E19">
+        <v>-2.5501</v>
+      </c>
+      <c r="F19">
+        <v>1.0999</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>2.82</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.107</v>
+      </c>
+      <c r="K19">
+        <v>0.094</v>
+      </c>
+      <c r="L19">
+        <v>0.013</v>
+      </c>
+      <c r="M19">
+        <v>0.26265612</v>
+      </c>
+      <c r="N19">
+        <v>-0.24965612</v>
+      </c>
+      <c r="O19">
+        <v>-0.04743466279999999</v>
+      </c>
+      <c r="P19">
+        <v>-0.2022214572</v>
+      </c>
+      <c r="Q19">
+        <v>-0.1082214572</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08428234049872307</v>
+      </c>
+      <c r="T19">
+        <v>0.6167248259411401</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.009403930888798626</v>
+      </c>
+      <c r="W19">
+        <v>0.2365543413037549</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.04949437309894023</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1121685806355785</v>
+      </c>
+      <c r="C20">
+        <v>2.515633474230227</v>
+      </c>
+      <c r="D20">
+        <v>3.680233474230227</v>
+      </c>
+      <c r="E20">
+        <v>-2.4854</v>
+      </c>
+      <c r="F20">
+        <v>1.1646</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>2.82</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.107</v>
+      </c>
+      <c r="K20">
+        <v>0.094</v>
+      </c>
+      <c r="L20">
+        <v>0.013</v>
+      </c>
+      <c r="M20">
+        <v>0.27810648</v>
+      </c>
+      <c r="N20">
+        <v>-0.26510648</v>
+      </c>
+      <c r="O20">
+        <v>-0.05037023119999998</v>
+      </c>
+      <c r="P20">
+        <v>-0.2147362488</v>
+      </c>
+      <c r="Q20">
+        <v>-0.1207362488</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08483700318773191</v>
+      </c>
+      <c r="T20">
+        <v>0.6242458604038369</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.008881490283865371</v>
+      </c>
+      <c r="W20">
+        <v>0.236679100120213</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.04674468570455459</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1141685806355785</v>
+      </c>
+      <c r="C21">
+        <v>2.35327385418179</v>
+      </c>
+      <c r="D21">
+        <v>3.58257385418179</v>
+      </c>
+      <c r="E21">
+        <v>-2.4207</v>
+      </c>
+      <c r="F21">
+        <v>1.2293</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>2.82</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.107</v>
+      </c>
+      <c r="K21">
+        <v>0.094</v>
+      </c>
+      <c r="L21">
+        <v>0.013</v>
+      </c>
+      <c r="M21">
+        <v>0.29355684</v>
+      </c>
+      <c r="N21">
+        <v>-0.28055684</v>
+      </c>
+      <c r="O21">
+        <v>-0.05330579959999999</v>
+      </c>
+      <c r="P21">
+        <v>-0.2272510404</v>
+      </c>
+      <c r="Q21">
+        <v>-0.1332510404</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08540536125177797</v>
+      </c>
+      <c r="T21">
+        <v>0.6319525994211682</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.008414043426819824</v>
+      </c>
+      <c r="W21">
+        <v>0.2367907264296754</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.04428443908852542</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1161685806355785</v>
+      </c>
+      <c r="C22">
+        <v>2.195963292510601</v>
+      </c>
+      <c r="D22">
+        <v>3.489963292510601</v>
+      </c>
+      <c r="E22">
+        <v>-2.356</v>
+      </c>
+      <c r="F22">
+        <v>1.294</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>2.82</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.107</v>
+      </c>
+      <c r="K22">
+        <v>0.094</v>
+      </c>
+      <c r="L22">
+        <v>0.013</v>
+      </c>
+      <c r="M22">
+        <v>0.3090072</v>
+      </c>
+      <c r="N22">
+        <v>-0.2960072</v>
+      </c>
+      <c r="O22">
+        <v>-0.05624136799999999</v>
+      </c>
+      <c r="P22">
+        <v>-0.239765832</v>
+      </c>
+      <c r="Q22">
+        <v>-0.145765832</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.0859879282674252</v>
+      </c>
+      <c r="T22">
+        <v>0.6398520069139328</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.007993341255478832</v>
+      </c>
+      <c r="W22">
+        <v>0.2368911901081917</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.0420702171340992</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1181685806355785</v>
+      </c>
+      <c r="C23">
+        <v>2.043320097242067</v>
+      </c>
+      <c r="D23">
+        <v>3.402020097242067</v>
+      </c>
+      <c r="E23">
+        <v>-2.2913</v>
+      </c>
+      <c r="F23">
+        <v>1.3587</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>2.82</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.107</v>
+      </c>
+      <c r="K23">
+        <v>0.094</v>
+      </c>
+      <c r="L23">
+        <v>0.013</v>
+      </c>
+      <c r="M23">
+        <v>0.32445756</v>
+      </c>
+      <c r="N23">
+        <v>-0.31145756</v>
+      </c>
+      <c r="O23">
+        <v>-0.05917693639999998</v>
+      </c>
+      <c r="P23">
+        <v>-0.2522806236</v>
+      </c>
+      <c r="Q23">
+        <v>-0.1582806236</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08658524381511412</v>
+      </c>
+      <c r="T23">
+        <v>0.6479513994065144</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.007612705957598889</v>
+      </c>
+      <c r="W23">
+        <v>0.2369820858173254</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.04006687346104687</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1201685806355785</v>
+      </c>
+      <c r="C24">
+        <v>1.895000103611391</v>
+      </c>
+      <c r="D24">
+        <v>3.318400103611391</v>
+      </c>
+      <c r="E24">
+        <v>-2.2266</v>
+      </c>
+      <c r="F24">
+        <v>1.4234</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>2.82</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.107</v>
+      </c>
+      <c r="K24">
+        <v>0.094</v>
+      </c>
+      <c r="L24">
+        <v>0.013</v>
+      </c>
+      <c r="M24">
+        <v>0.33990792</v>
+      </c>
+      <c r="N24">
+        <v>-0.32690792</v>
+      </c>
+      <c r="O24">
+        <v>-0.06211250479999999</v>
+      </c>
+      <c r="P24">
+        <v>-0.2647954152000001</v>
+      </c>
+      <c r="Q24">
+        <v>-0.1707954152000001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.08719787514607713</v>
+      </c>
+      <c r="T24">
+        <v>0.6562584686296746</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.00726667386861712</v>
+      </c>
+      <c r="W24">
+        <v>0.2370647182801743</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.03824565194009011</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1221685806355785</v>
+      </c>
+      <c r="C25">
+        <v>1.750692172702341</v>
+      </c>
+      <c r="D25">
+        <v>3.238792172702341</v>
+      </c>
+      <c r="E25">
+        <v>-2.1619</v>
+      </c>
+      <c r="F25">
+        <v>1.4881</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>2.82</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.107</v>
+      </c>
+      <c r="K25">
+        <v>0.094</v>
+      </c>
+      <c r="L25">
+        <v>0.013</v>
+      </c>
+      <c r="M25">
+        <v>0.35535828</v>
+      </c>
+      <c r="N25">
+        <v>-0.34235828</v>
+      </c>
+      <c r="O25">
+        <v>-0.06504807319999999</v>
+      </c>
+      <c r="P25">
+        <v>-0.2773102068</v>
+      </c>
+      <c r="Q25">
+        <v>-0.1833102068</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.08782641897914306</v>
+      </c>
+      <c r="T25">
+        <v>0.6647813058846056</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.006950731526503333</v>
+      </c>
+      <c r="W25">
+        <v>0.237140165311471</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.03658279750791238</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1241685806355785</v>
+      </c>
+      <c r="C26">
+        <v>1.610114322828554</v>
+      </c>
+      <c r="D26">
+        <v>3.162914322828554</v>
+      </c>
+      <c r="E26">
+        <v>-2.0972</v>
+      </c>
+      <c r="F26">
+        <v>1.5528</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>2.82</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.107</v>
+      </c>
+      <c r="K26">
+        <v>0.094</v>
+      </c>
+      <c r="L26">
+        <v>0.013</v>
+      </c>
+      <c r="M26">
+        <v>0.37080864</v>
+      </c>
+      <c r="N26">
+        <v>-0.35780864</v>
+      </c>
+      <c r="O26">
+        <v>-0.06798364159999998</v>
+      </c>
+      <c r="P26">
+        <v>-0.2898249984</v>
+      </c>
+      <c r="Q26">
+        <v>-0.1958249984</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.08847150343939494</v>
+      </c>
+      <c r="T26">
+        <v>0.6735284283304556</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.006661117712899027</v>
+      </c>
+      <c r="W26">
+        <v>0.2372093250901597</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.035058514278416</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1261685806355785</v>
+      </c>
+      <c r="C27">
+        <v>1.473010392266345</v>
+      </c>
+      <c r="D27">
+        <v>3.090510392266345</v>
+      </c>
+      <c r="E27">
+        <v>-2.0325</v>
+      </c>
+      <c r="F27">
+        <v>1.6175</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>2.82</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.107</v>
+      </c>
+      <c r="K27">
+        <v>0.094</v>
+      </c>
+      <c r="L27">
+        <v>0.013</v>
+      </c>
+      <c r="M27">
+        <v>0.386259</v>
+      </c>
+      <c r="N27">
+        <v>-0.373259</v>
+      </c>
+      <c r="O27">
+        <v>-0.07091920999999998</v>
+      </c>
+      <c r="P27">
+        <v>-0.30233979</v>
+      </c>
+      <c r="Q27">
+        <v>-0.20833979</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.08913379015192022</v>
+      </c>
+      <c r="T27">
+        <v>0.6825088073748617</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.006394673004383066</v>
+      </c>
+      <c r="W27">
+        <v>0.2372729520865534</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.03365617370727936</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1281685806355785</v>
+      </c>
+      <c r="C28">
+        <v>1.339147150100318</v>
+      </c>
+      <c r="D28">
+        <v>3.021347150100318</v>
+      </c>
+      <c r="E28">
+        <v>-1.9678</v>
+      </c>
+      <c r="F28">
+        <v>1.6822</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>2.82</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.107</v>
+      </c>
+      <c r="K28">
+        <v>0.094</v>
+      </c>
+      <c r="L28">
+        <v>0.013</v>
+      </c>
+      <c r="M28">
+        <v>0.40170936</v>
+      </c>
+      <c r="N28">
+        <v>-0.38870936</v>
+      </c>
+      <c r="O28">
+        <v>-0.07385477839999997</v>
+      </c>
+      <c r="P28">
+        <v>-0.3148545816</v>
+      </c>
+      <c r="Q28">
+        <v>-0.2208545816</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.08981397650532454</v>
+      </c>
+      <c r="T28">
+        <v>0.6917318993664139</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.006148724042676025</v>
+      </c>
+      <c r="W28">
+        <v>0.237331684698609</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.03236170548776862</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1301685806355785</v>
+      </c>
+      <c r="C29">
+        <v>1.208311786519462</v>
+      </c>
+      <c r="D29">
+        <v>2.955211786519462</v>
+      </c>
+      <c r="E29">
+        <v>-1.9031</v>
+      </c>
+      <c r="F29">
+        <v>1.7469</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>2.82</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.107</v>
+      </c>
+      <c r="K29">
+        <v>0.094</v>
+      </c>
+      <c r="L29">
+        <v>0.013</v>
+      </c>
+      <c r="M29">
+        <v>0.4171597200000001</v>
+      </c>
+      <c r="N29">
+        <v>-0.4041597200000001</v>
+      </c>
+      <c r="O29">
+        <v>-0.07679034679999999</v>
+      </c>
+      <c r="P29">
+        <v>-0.3273693732</v>
+      </c>
+      <c r="Q29">
+        <v>-0.2333693732</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09051279810128789</v>
+      </c>
+      <c r="T29">
+        <v>0.7012076788097894</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.005920993522576912</v>
+      </c>
+      <c r="W29">
+        <v>0.2373860667468086</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.03116312380303643</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1321685806355785</v>
+      </c>
+      <c r="C30">
+        <v>1.08030972566767</v>
+      </c>
+      <c r="D30">
+        <v>2.89190972566767</v>
+      </c>
+      <c r="E30">
+        <v>-1.8384</v>
+      </c>
+      <c r="F30">
+        <v>1.8116</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>2.82</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.107</v>
+      </c>
+      <c r="K30">
+        <v>0.094</v>
+      </c>
+      <c r="L30">
+        <v>0.013</v>
+      </c>
+      <c r="M30">
+        <v>0.4326100800000001</v>
+      </c>
+      <c r="N30">
+        <v>-0.4196100800000001</v>
+      </c>
+      <c r="O30">
+        <v>-0.07972591519999998</v>
+      </c>
+      <c r="P30">
+        <v>-0.3398841648000001</v>
+      </c>
+      <c r="Q30">
+        <v>-0.2458841648000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09123103140825023</v>
+      </c>
+      <c r="T30">
+        <v>0.7109466743488143</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.005709529468199166</v>
+      </c>
+      <c r="W30">
+        <v>0.2374365643629941</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.03005015509578512</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1341685806355785</v>
+      </c>
+      <c r="C31">
+        <v>0.9549627136980108</v>
+      </c>
+      <c r="D31">
+        <v>2.831262713698011</v>
+      </c>
+      <c r="E31">
+        <v>-1.7737</v>
+      </c>
+      <c r="F31">
+        <v>1.8763</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>2.82</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.107</v>
+      </c>
+      <c r="K31">
+        <v>0.094</v>
+      </c>
+      <c r="L31">
+        <v>0.013</v>
+      </c>
+      <c r="M31">
+        <v>0.44806044</v>
+      </c>
+      <c r="N31">
+        <v>-0.43506044</v>
+      </c>
+      <c r="O31">
+        <v>-0.08266148359999997</v>
+      </c>
+      <c r="P31">
+        <v>-0.3523989564</v>
+      </c>
+      <c r="Q31">
+        <v>-0.2583989564</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09196949663935233</v>
+      </c>
+      <c r="T31">
+        <v>0.7209600077903469</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.00551264914170954</v>
+      </c>
+      <c r="W31">
+        <v>0.2374835793849598</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.02901394285110293</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1361685806355785</v>
+      </c>
+      <c r="C32">
+        <v>0.8321071424610311</v>
+      </c>
+      <c r="D32">
+        <v>2.773107142461031</v>
+      </c>
+      <c r="E32">
+        <v>-1.709</v>
+      </c>
+      <c r="F32">
+        <v>1.941</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>2.82</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.107</v>
+      </c>
+      <c r="K32">
+        <v>0.094</v>
+      </c>
+      <c r="L32">
+        <v>0.013</v>
+      </c>
+      <c r="M32">
+        <v>0.4635108</v>
+      </c>
+      <c r="N32">
+        <v>-0.4505108</v>
+      </c>
+      <c r="O32">
+        <v>-0.08559705199999998</v>
+      </c>
+      <c r="P32">
+        <v>-0.364913748</v>
+      </c>
+      <c r="Q32">
+        <v>-0.270913748</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09272906087705737</v>
+      </c>
+      <c r="T32">
+        <v>0.7312594364730661</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.005328894170319222</v>
+      </c>
+      <c r="W32">
+        <v>0.2375274600721278</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.0280468114227328</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1381685806355785</v>
+      </c>
+      <c r="C33">
+        <v>0.711592575628663</v>
+      </c>
+      <c r="D33">
+        <v>2.717292575628663</v>
+      </c>
+      <c r="E33">
+        <v>-1.6443</v>
+      </c>
+      <c r="F33">
+        <v>2.0057</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>2.82</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.107</v>
+      </c>
+      <c r="K33">
+        <v>0.094</v>
+      </c>
+      <c r="L33">
+        <v>0.013</v>
+      </c>
+      <c r="M33">
+        <v>0.4789611600000001</v>
+      </c>
+      <c r="N33">
+        <v>-0.46596116</v>
+      </c>
+      <c r="O33">
+        <v>-0.08853262039999998</v>
+      </c>
+      <c r="P33">
+        <v>-0.3774285396000001</v>
+      </c>
+      <c r="Q33">
+        <v>-0.2834285396</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09351064146947849</v>
+      </c>
+      <c r="T33">
+        <v>0.7418573993205019</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.00515699435837344</v>
+      </c>
+      <c r="W33">
+        <v>0.2375685097472204</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.02714207557038661</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1401685806355785</v>
+      </c>
+      <c r="C34">
+        <v>0.593280449295408</v>
+      </c>
+      <c r="D34">
+        <v>2.663680449295408</v>
+      </c>
+      <c r="E34">
+        <v>-1.5796</v>
+      </c>
+      <c r="F34">
+        <v>2.0704</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>2.82</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.107</v>
+      </c>
+      <c r="K34">
+        <v>0.094</v>
+      </c>
+      <c r="L34">
+        <v>0.013</v>
+      </c>
+      <c r="M34">
+        <v>0.49441152</v>
+      </c>
+      <c r="N34">
+        <v>-0.48141152</v>
+      </c>
+      <c r="O34">
+        <v>-0.09146818879999997</v>
+      </c>
+      <c r="P34">
+        <v>-0.3899433312</v>
+      </c>
+      <c r="Q34">
+        <v>-0.2959433312</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09431520972638259</v>
+      </c>
+      <c r="T34">
+        <v>0.7527670669575681</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.004995838284674271</v>
+      </c>
+      <c r="W34">
+        <v>0.2376069938176198</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.02629388570881197</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1421685806355785</v>
+      </c>
+      <c r="C35">
+        <v>0.4770429234259943</v>
+      </c>
+      <c r="D35">
+        <v>2.612142923425994</v>
+      </c>
+      <c r="E35">
+        <v>-1.5149</v>
+      </c>
+      <c r="F35">
+        <v>2.1351</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>2.82</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.107</v>
+      </c>
+      <c r="K35">
+        <v>0.094</v>
+      </c>
+      <c r="L35">
+        <v>0.013</v>
+      </c>
+      <c r="M35">
+        <v>0.50986188</v>
+      </c>
+      <c r="N35">
+        <v>-0.49686188</v>
+      </c>
+      <c r="O35">
+        <v>-0.09440375719999997</v>
+      </c>
+      <c r="P35">
+        <v>-0.4024581228</v>
+      </c>
+      <c r="Q35">
+        <v>-0.3084581228000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09514379494617933</v>
+      </c>
+      <c r="T35">
+        <v>0.7640023963151437</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.004844449245744747</v>
+      </c>
+      <c r="W35">
+        <v>0.2376431455201161</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.02549710129339344</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1441685806355785</v>
+      </c>
+      <c r="C36">
+        <v>0.3627618641069885</v>
+      </c>
+      <c r="D36">
+        <v>2.562561864106989</v>
+      </c>
+      <c r="E36">
+        <v>-1.4502</v>
+      </c>
+      <c r="F36">
+        <v>2.1998</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>2.82</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.107</v>
+      </c>
+      <c r="K36">
+        <v>0.094</v>
+      </c>
+      <c r="L36">
+        <v>0.013</v>
+      </c>
+      <c r="M36">
+        <v>0.5253122400000001</v>
+      </c>
+      <c r="N36">
+        <v>-0.5123122400000001</v>
+      </c>
+      <c r="O36">
+        <v>-0.09733932559999998</v>
+      </c>
+      <c r="P36">
+        <v>-0.4149729144000001</v>
+      </c>
+      <c r="Q36">
+        <v>-0.3209729144000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09599748880900025</v>
+      </c>
+      <c r="T36">
+        <v>0.7755781901987066</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.004701965444399313</v>
+      </c>
+      <c r="W36">
+        <v>0.2376771706518775</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.02474718654947006</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1461685806355785</v>
+      </c>
+      <c r="C37">
+        <v>0.2503279395466058</v>
+      </c>
+      <c r="D37">
+        <v>2.514827939546606</v>
+      </c>
+      <c r="E37">
+        <v>-1.3855</v>
+      </c>
+      <c r="F37">
+        <v>2.2645</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>2.82</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.107</v>
+      </c>
+      <c r="K37">
+        <v>0.094</v>
+      </c>
+      <c r="L37">
+        <v>0.013</v>
+      </c>
+      <c r="M37">
+        <v>0.5407626</v>
+      </c>
+      <c r="N37">
+        <v>-0.5277626</v>
+      </c>
+      <c r="O37">
+        <v>-0.100274894</v>
+      </c>
+      <c r="P37">
+        <v>-0.427487706</v>
+      </c>
+      <c r="Q37">
+        <v>-0.333487706</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.09687745017529256</v>
+      </c>
+      <c r="T37">
+        <v>0.7875101623556097</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.004567623574559334</v>
+      </c>
+      <c r="W37">
+        <v>0.2377092514903953</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.02404012407662814</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1481685806355785</v>
+      </c>
+      <c r="C38">
+        <v>0.1396398152620626</v>
+      </c>
+      <c r="D38">
+        <v>2.468839815262062</v>
+      </c>
+      <c r="E38">
+        <v>-1.3208</v>
+      </c>
+      <c r="F38">
+        <v>2.3292</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>2.82</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.107</v>
+      </c>
+      <c r="K38">
+        <v>0.094</v>
+      </c>
+      <c r="L38">
+        <v>0.013</v>
+      </c>
+      <c r="M38">
+        <v>0.55621296</v>
+      </c>
+      <c r="N38">
+        <v>-0.54321296</v>
+      </c>
+      <c r="O38">
+        <v>-0.1032104624</v>
+      </c>
+      <c r="P38">
+        <v>-0.4400024976</v>
+      </c>
+      <c r="Q38">
+        <v>-0.3460024976</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.09778491033428149</v>
+      </c>
+      <c r="T38">
+        <v>0.7998150086424161</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.004440745141932686</v>
+      </c>
+      <c r="W38">
+        <v>0.2377395500601065</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.02337234285227729</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1501685806355785</v>
+      </c>
+      <c r="C39">
+        <v>0.030603435985745</v>
+      </c>
+      <c r="D39">
+        <v>2.424503435985745</v>
+      </c>
+      <c r="E39">
+        <v>-1.2561</v>
+      </c>
+      <c r="F39">
+        <v>2.3939</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>2.82</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.107</v>
+      </c>
+      <c r="K39">
+        <v>0.094</v>
+      </c>
+      <c r="L39">
+        <v>0.013</v>
+      </c>
+      <c r="M39">
+        <v>0.57166332</v>
+      </c>
+      <c r="N39">
+        <v>-0.55866332</v>
+      </c>
+      <c r="O39">
+        <v>-0.1061460308</v>
+      </c>
+      <c r="P39">
+        <v>-0.4525172892</v>
+      </c>
+      <c r="Q39">
+        <v>-0.3585172892</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.09872117875228598</v>
+      </c>
+      <c r="T39">
+        <v>0.8125104849700735</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.004320725002961531</v>
+      </c>
+      <c r="W39">
+        <v>0.2377682108692928</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.02274065791032387</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1521685806355785</v>
+      </c>
+      <c r="C40">
+        <v>-0.07686861641877885</v>
+      </c>
+      <c r="D40">
+        <v>2.381731383581221</v>
+      </c>
+      <c r="E40">
+        <v>-1.1914</v>
+      </c>
+      <c r="F40">
+        <v>2.4586</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>2.82</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.107</v>
+      </c>
+      <c r="K40">
+        <v>0.094</v>
+      </c>
+      <c r="L40">
+        <v>0.013</v>
+      </c>
+      <c r="M40">
+        <v>0.5871136800000001</v>
+      </c>
+      <c r="N40">
+        <v>-0.5741136800000001</v>
+      </c>
+      <c r="O40">
+        <v>-0.1090815992</v>
+      </c>
+      <c r="P40">
+        <v>-0.4650320808000001</v>
+      </c>
+      <c r="Q40">
+        <v>-0.3710320808000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.09968764937732284</v>
+      </c>
+      <c r="T40">
+        <v>0.8256154927921715</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.004207021713409912</v>
+      </c>
+      <c r="W40">
+        <v>0.2377953632148377</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.02214221954426276</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1541685806355785</v>
+      </c>
+      <c r="C41">
+        <v>-0.1828576982547521</v>
+      </c>
+      <c r="D41">
+        <v>2.340442301745248</v>
+      </c>
+      <c r="E41">
+        <v>-1.1267</v>
+      </c>
+      <c r="F41">
+        <v>2.5233</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>2.82</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.107</v>
+      </c>
+      <c r="K41">
+        <v>0.094</v>
+      </c>
+      <c r="L41">
+        <v>0.013</v>
+      </c>
+      <c r="M41">
+        <v>0.60256404</v>
+      </c>
+      <c r="N41">
+        <v>-0.58956404</v>
+      </c>
+      <c r="O41">
+        <v>-0.1120171676</v>
+      </c>
+      <c r="P41">
+        <v>-0.4775468724</v>
+      </c>
+      <c r="Q41">
+        <v>-0.3835468724</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1006858075638363</v>
+      </c>
+      <c r="T41">
+        <v>0.8391501730018791</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.004099149361784018</v>
+      </c>
+      <c r="W41">
+        <v>0.237821123132406</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.02157447032517912</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1561685806355785</v>
+      </c>
+      <c r="C42">
+        <v>-0.2874396204705829</v>
+      </c>
+      <c r="D42">
+        <v>2.300560379529417</v>
+      </c>
+      <c r="E42">
+        <v>-1.062</v>
+      </c>
+      <c r="F42">
+        <v>2.588</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>2.82</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.107</v>
+      </c>
+      <c r="K42">
+        <v>0.094</v>
+      </c>
+      <c r="L42">
+        <v>0.013</v>
+      </c>
+      <c r="M42">
+        <v>0.6180144000000001</v>
+      </c>
+      <c r="N42">
+        <v>-0.6050144000000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.114952736</v>
+      </c>
+      <c r="P42">
+        <v>-0.4900616640000001</v>
+      </c>
+      <c r="Q42">
+        <v>-0.3960616640000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1017172376899003</v>
+      </c>
+      <c r="T42">
+        <v>0.8531360092185772</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.003996670627739416</v>
+      </c>
+      <c r="W42">
+        <v>0.2378455950540958</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.0210351085670496</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1581685806355785</v>
+      </c>
+      <c r="C43">
+        <v>-0.3906851132171676</v>
+      </c>
+      <c r="D43">
+        <v>2.262014886782833</v>
+      </c>
+      <c r="E43">
+        <v>-0.9972999999999996</v>
+      </c>
+      <c r="F43">
+        <v>2.6527</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>2.82</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.107</v>
+      </c>
+      <c r="K43">
+        <v>0.094</v>
+      </c>
+      <c r="L43">
+        <v>0.013</v>
+      </c>
+      <c r="M43">
+        <v>0.6334647600000001</v>
+      </c>
+      <c r="N43">
+        <v>-0.6204647600000001</v>
+      </c>
+      <c r="O43">
+        <v>-0.1178883044</v>
+      </c>
+      <c r="P43">
+        <v>-0.5025764556000001</v>
+      </c>
+      <c r="Q43">
+        <v>-0.4085764556000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1027836315490511</v>
+      </c>
+      <c r="T43">
+        <v>0.8675959415782141</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.003899190856331138</v>
+      </c>
+      <c r="W43">
+        <v>0.2378688732235081</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.02052205713858501</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1601685806355785</v>
+      </c>
+      <c r="C44">
+        <v>-0.4926602444733317</v>
+      </c>
+      <c r="D44">
+        <v>2.224739755526668</v>
+      </c>
+      <c r="E44">
+        <v>-0.9326000000000003</v>
+      </c>
+      <c r="F44">
+        <v>2.7174</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>2.82</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.107</v>
+      </c>
+      <c r="K44">
+        <v>0.094</v>
+      </c>
+      <c r="L44">
+        <v>0.013</v>
+      </c>
+      <c r="M44">
+        <v>0.64891512</v>
+      </c>
+      <c r="N44">
+        <v>-0.6359151199999999</v>
+      </c>
+      <c r="O44">
+        <v>-0.1208238728</v>
+      </c>
+      <c r="P44">
+        <v>-0.5150912472</v>
+      </c>
+      <c r="Q44">
+        <v>-0.4210912472</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1038867976102416</v>
+      </c>
+      <c r="T44">
+        <v>0.8825544922950797</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.003806352978799445</v>
+      </c>
+      <c r="W44">
+        <v>0.2378910429086627</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.02003343673052338</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1621685806355785</v>
+      </c>
+      <c r="C45">
+        <v>-0.5934267979517807</v>
+      </c>
+      <c r="D45">
+        <v>2.188673202048219</v>
+      </c>
+      <c r="E45">
+        <v>-0.8679000000000001</v>
+      </c>
+      <c r="F45">
+        <v>2.7821</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>2.82</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.107</v>
+      </c>
+      <c r="K45">
+        <v>0.094</v>
+      </c>
+      <c r="L45">
+        <v>0.013</v>
+      </c>
+      <c r="M45">
+        <v>0.66436548</v>
+      </c>
+      <c r="N45">
+        <v>-0.6513654799999999</v>
+      </c>
+      <c r="O45">
+        <v>-0.1237594412</v>
+      </c>
+      <c r="P45">
+        <v>-0.5276060388</v>
+      </c>
+      <c r="Q45">
+        <v>-0.4336060388</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1050286712525266</v>
+      </c>
+      <c r="T45">
+        <v>0.8980379044406075</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.003717833142083178</v>
+      </c>
+      <c r="W45">
+        <v>0.2379121814456706</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.01956754285306939</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1641685806355785</v>
+      </c>
+      <c r="C46">
+        <v>-0.6930426148327302</v>
+      </c>
+      <c r="D46">
+        <v>2.15375738516727</v>
+      </c>
+      <c r="E46">
+        <v>-0.8031999999999999</v>
+      </c>
+      <c r="F46">
+        <v>2.8468</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>2.82</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.107</v>
+      </c>
+      <c r="K46">
+        <v>0.094</v>
+      </c>
+      <c r="L46">
+        <v>0.013</v>
+      </c>
+      <c r="M46">
+        <v>0.6798158400000001</v>
+      </c>
+      <c r="N46">
+        <v>-0.66681584</v>
+      </c>
+      <c r="O46">
+        <v>-0.1266950096</v>
+      </c>
+      <c r="P46">
+        <v>-0.5401208304</v>
+      </c>
+      <c r="Q46">
+        <v>-0.4461208304000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1062113260963217</v>
+      </c>
+      <c r="T46">
+        <v>0.9140742955913326</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.00363333693430856</v>
+      </c>
+      <c r="W46">
+        <v>0.2379323591400871</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.01912282597004511</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1661685806355785</v>
+      </c>
+      <c r="C47">
+        <v>-0.7915619033012025</v>
+      </c>
+      <c r="D47">
+        <v>2.119938096698797</v>
+      </c>
+      <c r="E47">
+        <v>-0.7385000000000002</v>
+      </c>
+      <c r="F47">
+        <v>2.9115</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>2.82</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.107</v>
+      </c>
+      <c r="K47">
+        <v>0.094</v>
+      </c>
+      <c r="L47">
+        <v>0.013</v>
+      </c>
+      <c r="M47">
+        <v>0.6952661999999999</v>
+      </c>
+      <c r="N47">
+        <v>-0.6822661999999999</v>
+      </c>
+      <c r="O47">
+        <v>-0.1296305779999999</v>
+      </c>
+      <c r="P47">
+        <v>-0.5526356219999999</v>
+      </c>
+      <c r="Q47">
+        <v>-0.458635622</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1074369865708003</v>
+      </c>
+      <c r="T47">
+        <v>0.9306938282384477</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.003552596113546148</v>
+      </c>
+      <c r="W47">
+        <v>0.2379516400480852</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.0186978742818219</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1681685806355785</v>
+      </c>
+      <c r="C48">
+        <v>-0.8890355193721797</v>
+      </c>
+      <c r="D48">
+        <v>2.08716448062782</v>
+      </c>
+      <c r="E48">
+        <v>-0.6738</v>
+      </c>
+      <c r="F48">
+        <v>2.9762</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>2.82</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.107</v>
+      </c>
+      <c r="K48">
+        <v>0.094</v>
+      </c>
+      <c r="L48">
+        <v>0.013</v>
+      </c>
+      <c r="M48">
+        <v>0.7107165600000001</v>
+      </c>
+      <c r="N48">
+        <v>-0.69771656</v>
+      </c>
+      <c r="O48">
+        <v>-0.1325661464</v>
+      </c>
+      <c r="P48">
+        <v>-0.5651504136000001</v>
+      </c>
+      <c r="Q48">
+        <v>-0.4711504136000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.108708041877667</v>
+      </c>
+      <c r="T48">
+        <v>0.9479288991317523</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.003475365763251667</v>
+      </c>
+      <c r="W48">
+        <v>0.2379700826557355</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.01829139875395613</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1701685806355785</v>
+      </c>
+      <c r="C49">
+        <v>-0.9855112220634905</v>
+      </c>
+      <c r="D49">
+        <v>2.05538877793651</v>
+      </c>
+      <c r="E49">
+        <v>-0.6090999999999998</v>
+      </c>
+      <c r="F49">
+        <v>3.0409</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>2.82</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.107</v>
+      </c>
+      <c r="K49">
+        <v>0.094</v>
+      </c>
+      <c r="L49">
+        <v>0.013</v>
+      </c>
+      <c r="M49">
+        <v>0.72616692</v>
+      </c>
+      <c r="N49">
+        <v>-0.71316692</v>
+      </c>
+      <c r="O49">
+        <v>-0.1355017148</v>
+      </c>
+      <c r="P49">
+        <v>-0.5776652052000001</v>
+      </c>
+      <c r="Q49">
+        <v>-0.4836652052000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1100270615357361</v>
+      </c>
+      <c r="T49">
+        <v>0.9658143500587666</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.003401421810842056</v>
+      </c>
+      <c r="W49">
+        <v>0.2379877404715709</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.01790222005706343</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1721685806355785</v>
+      </c>
+      <c r="C50">
+        <v>-1.081033905609216</v>
+      </c>
+      <c r="D50">
+        <v>2.024566094390784</v>
+      </c>
+      <c r="E50">
+        <v>-0.5444</v>
+      </c>
+      <c r="F50">
+        <v>3.1056</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>2.82</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.107</v>
+      </c>
+      <c r="K50">
+        <v>0.094</v>
+      </c>
+      <c r="L50">
+        <v>0.013</v>
+      </c>
+      <c r="M50">
+        <v>0.74161728</v>
+      </c>
+      <c r="N50">
+        <v>-0.72861728</v>
+      </c>
+      <c r="O50">
+        <v>-0.1384372832</v>
+      </c>
+      <c r="P50">
+        <v>-0.5901799968000001</v>
+      </c>
+      <c r="Q50">
+        <v>-0.4961799968000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1113968127191157</v>
+      </c>
+      <c r="T50">
+        <v>0.9843877029445119</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.003330558856449514</v>
+      </c>
+      <c r="W50">
+        <v>0.2380046625450799</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.01752925713920794</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1741685806355785</v>
+      </c>
+      <c r="C51">
+        <v>-1.175645811088095</v>
+      </c>
+      <c r="D51">
+        <v>1.994654188911904</v>
+      </c>
+      <c r="E51">
+        <v>-0.4797000000000002</v>
+      </c>
+      <c r="F51">
+        <v>3.1703</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>2.82</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.107</v>
+      </c>
+      <c r="K51">
+        <v>0.094</v>
+      </c>
+      <c r="L51">
+        <v>0.013</v>
+      </c>
+      <c r="M51">
+        <v>0.7570676399999999</v>
+      </c>
+      <c r="N51">
+        <v>-0.7440676399999999</v>
+      </c>
+      <c r="O51">
+        <v>-0.1413728515999999</v>
+      </c>
+      <c r="P51">
+        <v>-0.6026947884</v>
+      </c>
+      <c r="Q51">
+        <v>-0.5086947884</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1128202796351768</v>
+      </c>
+      <c r="T51">
+        <v>1.003689422610091</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.003262588267542381</v>
+      </c>
+      <c r="W51">
+        <v>0.2380208939217109</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.01717151719759147</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1761685806355785</v>
+      </c>
+      <c r="C52">
+        <v>-1.269386719564882</v>
+      </c>
+      <c r="D52">
+        <v>1.965613280435118</v>
+      </c>
+      <c r="E52">
+        <v>-0.415</v>
+      </c>
+      <c r="F52">
+        <v>3.235</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>2.82</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.107</v>
+      </c>
+      <c r="K52">
+        <v>0.094</v>
+      </c>
+      <c r="L52">
+        <v>0.013</v>
+      </c>
+      <c r="M52">
+        <v>0.772518</v>
+      </c>
+      <c r="N52">
+        <v>-0.759518</v>
+      </c>
+      <c r="O52">
+        <v>-0.14430842</v>
+      </c>
+      <c r="P52">
+        <v>-0.61520958</v>
+      </c>
+      <c r="Q52">
+        <v>-0.5212095800000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1143006852278803</v>
+      </c>
+      <c r="T52">
+        <v>1.023763211062293</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.003197336502191533</v>
+      </c>
+      <c r="W52">
+        <v>0.2380364760432767</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.01682808685363968</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1781685806355785</v>
+      </c>
+      <c r="C53">
+        <v>-1.362294128601712</v>
+      </c>
+      <c r="D53">
+        <v>1.937405871398288</v>
+      </c>
+      <c r="E53">
+        <v>-0.3502999999999998</v>
+      </c>
+      <c r="F53">
+        <v>3.2997</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>2.82</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.107</v>
+      </c>
+      <c r="K53">
+        <v>0.094</v>
+      </c>
+      <c r="L53">
+        <v>0.013</v>
+      </c>
+      <c r="M53">
+        <v>0.78796836</v>
+      </c>
+      <c r="N53">
+        <v>-0.77496836</v>
+      </c>
+      <c r="O53">
+        <v>-0.1472439884</v>
+      </c>
+      <c r="P53">
+        <v>-0.6277243716000001</v>
+      </c>
+      <c r="Q53">
+        <v>-0.5337243716000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1158415155386534</v>
+      </c>
+      <c r="T53">
+        <v>1.044656337818666</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.003134643629599543</v>
+      </c>
+      <c r="W53">
+        <v>0.2380514471012516</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.01649812436631337</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1801685806355785</v>
+      </c>
+      <c r="C54">
+        <v>-1.45440341378641</v>
+      </c>
+      <c r="D54">
+        <v>1.90999658621359</v>
+      </c>
+      <c r="E54">
+        <v>-0.2856000000000001</v>
+      </c>
+      <c r="F54">
+        <v>3.3644</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>2.82</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.107</v>
+      </c>
+      <c r="K54">
+        <v>0.094</v>
+      </c>
+      <c r="L54">
+        <v>0.013</v>
+      </c>
+      <c r="M54">
+        <v>0.80341872</v>
+      </c>
+      <c r="N54">
+        <v>-0.79041872</v>
+      </c>
+      <c r="O54">
+        <v>-0.1501795568</v>
+      </c>
+      <c r="P54">
+        <v>-0.6402391632000001</v>
+      </c>
+      <c r="Q54">
+        <v>-0.5462391632000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1174465471123753</v>
+      </c>
+      <c r="T54">
+        <v>1.066420011523221</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.003074362021338013</v>
+      </c>
+      <c r="W54">
+        <v>0.2380658423493045</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.01618085274388426</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1821685806355785</v>
+      </c>
+      <c r="C55">
+        <v>-1.545747976740808</v>
+      </c>
+      <c r="D55">
+        <v>1.883352023259192</v>
+      </c>
+      <c r="E55">
+        <v>-0.2208999999999999</v>
+      </c>
+      <c r="F55">
+        <v>3.4291</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>2.82</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.107</v>
+      </c>
+      <c r="K55">
+        <v>0.094</v>
+      </c>
+      <c r="L55">
+        <v>0.013</v>
+      </c>
+      <c r="M55">
+        <v>0.81886908</v>
+      </c>
+      <c r="N55">
+        <v>-0.80586908</v>
+      </c>
+      <c r="O55">
+        <v>-0.1531151252</v>
+      </c>
+      <c r="P55">
+        <v>-0.6527539548000001</v>
+      </c>
+      <c r="Q55">
+        <v>-0.5587539548000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1191198779020004</v>
+      </c>
+      <c r="T55">
+        <v>1.089109799002439</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.00301635519074673</v>
+      </c>
+      <c r="W55">
+        <v>0.2380796943804497</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.01587555363550908</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1841685806355785</v>
+      </c>
+      <c r="C56">
+        <v>-1.636359380911156</v>
+      </c>
+      <c r="D56">
+        <v>1.857440619088845</v>
+      </c>
+      <c r="E56">
+        <v>-0.1561999999999997</v>
+      </c>
+      <c r="F56">
+        <v>3.4938</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>2.82</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.107</v>
+      </c>
+      <c r="K56">
+        <v>0.094</v>
+      </c>
+      <c r="L56">
+        <v>0.013</v>
+      </c>
+      <c r="M56">
+        <v>0.8343194400000001</v>
+      </c>
+      <c r="N56">
+        <v>-0.8213194400000001</v>
+      </c>
+      <c r="O56">
+        <v>-0.1560506936</v>
+      </c>
+      <c r="P56">
+        <v>-0.6652687464000001</v>
+      </c>
+      <c r="Q56">
+        <v>-0.5712687464000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1208659622042177</v>
+      </c>
+      <c r="T56">
+        <v>1.112786098980753</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.002960496761288456</v>
+      </c>
+      <c r="W56">
+        <v>0.2380930333734043</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.01558156190151816</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1861685806355785</v>
+      </c>
+      <c r="C57">
+        <v>-1.72626747630134</v>
+      </c>
+      <c r="D57">
+        <v>1.83223252369866</v>
+      </c>
+      <c r="E57">
+        <v>-0.09149999999999991</v>
+      </c>
+      <c r="F57">
+        <v>3.5585</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>2.82</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.107</v>
+      </c>
+      <c r="K57">
+        <v>0.094</v>
+      </c>
+      <c r="L57">
+        <v>0.013</v>
+      </c>
+      <c r="M57">
+        <v>0.8497698</v>
+      </c>
+      <c r="N57">
+        <v>-0.8367698</v>
+      </c>
+      <c r="O57">
+        <v>-0.158986262</v>
+      </c>
+      <c r="P57">
+        <v>-0.677783538</v>
+      </c>
+      <c r="Q57">
+        <v>-0.583783538</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1226896502532004</v>
+      </c>
+      <c r="T57">
+        <v>1.137514678958103</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.002906669547446848</v>
+      </c>
+      <c r="W57">
+        <v>0.2381058873120697</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.01529826077603602</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1881685806355785</v>
+      </c>
+      <c r="C58">
+        <v>-1.815500514185242</v>
+      </c>
+      <c r="D58">
+        <v>1.807699485814758</v>
+      </c>
+      <c r="E58">
+        <v>-0.02679999999999971</v>
+      </c>
+      <c r="F58">
+        <v>3.6232</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>2.82</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.107</v>
+      </c>
+      <c r="K58">
+        <v>0.094</v>
+      </c>
+      <c r="L58">
+        <v>0.013</v>
+      </c>
+      <c r="M58">
+        <v>0.8652201600000001</v>
+      </c>
+      <c r="N58">
+        <v>-0.8522201600000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.1619218304</v>
+      </c>
+      <c r="P58">
+        <v>-0.6902983296000001</v>
+      </c>
+      <c r="Q58">
+        <v>-0.5962983296000002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1245962332135004</v>
+      </c>
+      <c r="T58">
+        <v>1.16336728529806</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.002854764734099583</v>
+      </c>
+      <c r="W58">
+        <v>0.238118282181497</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.01502507754789251</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1901685806355785</v>
+      </c>
+      <c r="C59">
+        <v>-1.904085252725095</v>
+      </c>
+      <c r="D59">
+        <v>1.783814747274905</v>
+      </c>
+      <c r="E59">
+        <v>0.03790000000000049</v>
+      </c>
+      <c r="F59">
+        <v>3.6879</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>2.82</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.107</v>
+      </c>
+      <c r="K59">
+        <v>0.094</v>
+      </c>
+      <c r="L59">
+        <v>0.013</v>
+      </c>
+      <c r="M59">
+        <v>0.8806705200000001</v>
+      </c>
+      <c r="N59">
+        <v>-0.8676705200000001</v>
+      </c>
+      <c r="O59">
+        <v>-0.1648573988</v>
+      </c>
+      <c r="P59">
+        <v>-0.7028131212000002</v>
+      </c>
+      <c r="Q59">
+        <v>-0.6088131212000002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1265914944510236</v>
+      </c>
+      <c r="T59">
+        <v>1.190422338444526</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.002804681142273274</v>
+      </c>
+      <c r="W59">
+        <v>0.2381302421432251</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.01476147969617514</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1921685806355785</v>
+      </c>
+      <c r="C60">
+        <v>-1.992047054325951</v>
+      </c>
+      <c r="D60">
+        <v>1.760552945674049</v>
+      </c>
+      <c r="E60">
+        <v>0.1025999999999998</v>
+      </c>
+      <c r="F60">
+        <v>3.7526</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>2.82</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.107</v>
+      </c>
+      <c r="K60">
+        <v>0.094</v>
+      </c>
+      <c r="L60">
+        <v>0.013</v>
+      </c>
+      <c r="M60">
+        <v>0.89612088</v>
+      </c>
+      <c r="N60">
+        <v>-0.88312088</v>
+      </c>
+      <c r="O60">
+        <v>-0.1677929671999999</v>
+      </c>
+      <c r="P60">
+        <v>-0.7153279128000001</v>
+      </c>
+      <c r="Q60">
+        <v>-0.6213279128000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.128681768128429</v>
+      </c>
+      <c r="T60">
+        <v>1.21876572745511</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.00275632457085477</v>
+      </c>
+      <c r="W60">
+        <v>0.2381417896924799</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.01450697142555146</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1941685806355785</v>
+      </c>
+      <c r="C61">
+        <v>-2.079409975470909</v>
+      </c>
+      <c r="D61">
+        <v>1.73789002452909</v>
+      </c>
+      <c r="E61">
+        <v>0.1672999999999996</v>
+      </c>
+      <c r="F61">
+        <v>3.817299999999999</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>2.82</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.107</v>
+      </c>
+      <c r="K61">
+        <v>0.094</v>
+      </c>
+      <c r="L61">
+        <v>0.013</v>
+      </c>
+      <c r="M61">
+        <v>0.9115712399999999</v>
+      </c>
+      <c r="N61">
+        <v>-0.8985712399999999</v>
+      </c>
+      <c r="O61">
+        <v>-0.1707285355999999</v>
+      </c>
+      <c r="P61">
+        <v>-0.7278427044</v>
+      </c>
+      <c r="Q61">
+        <v>-0.6338427044</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1308740063754638</v>
+      </c>
+      <c r="T61">
+        <v>1.248491720807674</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.002709607205247063</v>
+      </c>
+      <c r="W61">
+        <v>0.238152945799387</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.01426109055393188</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1961685806355785</v>
+      </c>
+      <c r="C62">
+        <v>-2.166196849706035</v>
+      </c>
+      <c r="D62">
+        <v>1.715803150293965</v>
+      </c>
+      <c r="E62">
+        <v>0.2319999999999998</v>
+      </c>
+      <c r="F62">
+        <v>3.882</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>2.82</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.107</v>
+      </c>
+      <c r="K62">
+        <v>0.094</v>
+      </c>
+      <c r="L62">
+        <v>0.013</v>
+      </c>
+      <c r="M62">
+        <v>0.9270216</v>
+      </c>
+      <c r="N62">
+        <v>-0.9140216</v>
+      </c>
+      <c r="O62">
+        <v>-0.173664104</v>
+      </c>
+      <c r="P62">
+        <v>-0.740357496</v>
+      </c>
+      <c r="Q62">
+        <v>-0.646357496</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1331758565348504</v>
+      </c>
+      <c r="T62">
+        <v>1.279704013827866</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.002664447085159611</v>
+      </c>
+      <c r="W62">
+        <v>0.2381637300360639</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.0140234057113664</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1981685806355785</v>
+      </c>
+      <c r="C63">
+        <v>-2.252429364376758</v>
+      </c>
+      <c r="D63">
+        <v>1.694270635623242</v>
+      </c>
+      <c r="E63">
+        <v>0.2967</v>
+      </c>
+      <c r="F63">
+        <v>3.9467</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>2.82</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.107</v>
+      </c>
+      <c r="K63">
+        <v>0.094</v>
+      </c>
+      <c r="L63">
+        <v>0.013</v>
+      </c>
+      <c r="M63">
+        <v>0.94247196</v>
+      </c>
+      <c r="N63">
+        <v>-0.92947196</v>
+      </c>
+      <c r="O63">
+        <v>-0.1765996723999999</v>
+      </c>
+      <c r="P63">
+        <v>-0.7528722876</v>
+      </c>
+      <c r="Q63">
+        <v>-0.6588722876000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1355957502921543</v>
+      </c>
+      <c r="T63">
+        <v>1.312516937259349</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.002620767624747158</v>
+      </c>
+      <c r="W63">
+        <v>0.2381741606912104</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.0137935138144587</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2001685806355785</v>
+      </c>
+      <c r="C64">
+        <v>-2.338128131657849</v>
+      </c>
+      <c r="D64">
+        <v>1.673271868342151</v>
+      </c>
+      <c r="E64">
+        <v>0.3614000000000002</v>
+      </c>
+      <c r="F64">
+        <v>4.0114</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>2.82</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.107</v>
+      </c>
+      <c r="K64">
+        <v>0.094</v>
+      </c>
+      <c r="L64">
+        <v>0.013</v>
+      </c>
+      <c r="M64">
+        <v>0.9579223200000001</v>
+      </c>
+      <c r="N64">
+        <v>-0.9449223200000001</v>
+      </c>
+      <c r="O64">
+        <v>-0.1795352408</v>
+      </c>
+      <c r="P64">
+        <v>-0.7653870792000002</v>
+      </c>
+      <c r="Q64">
+        <v>-0.6713870792000002</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1381430068787899</v>
+      </c>
+      <c r="T64">
+        <v>1.347056856660911</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.00257849717918672</v>
+      </c>
+      <c r="W64">
+        <v>0.2381842548736102</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.01357103778519331</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2021685806355785</v>
+      </c>
+      <c r="C65">
+        <v>-2.423312754365989</v>
+      </c>
+      <c r="D65">
+        <v>1.652787245634011</v>
+      </c>
+      <c r="E65">
+        <v>0.4261000000000004</v>
+      </c>
+      <c r="F65">
+        <v>4.0761</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>2.82</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.107</v>
+      </c>
+      <c r="K65">
+        <v>0.094</v>
+      </c>
+      <c r="L65">
+        <v>0.013</v>
+      </c>
+      <c r="M65">
+        <v>0.9733726800000001</v>
+      </c>
+      <c r="N65">
+        <v>-0.9603726800000001</v>
+      </c>
+      <c r="O65">
+        <v>-0.1824708092</v>
+      </c>
+      <c r="P65">
+        <v>-0.7779018708000001</v>
+      </c>
+      <c r="Q65">
+        <v>-0.6839018708000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1408279530106491</v>
+      </c>
+      <c r="T65">
+        <v>1.383463798732828</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.002537568652532963</v>
+      </c>
+      <c r="W65">
+        <v>0.2381940286057752</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.01335562448701566</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2041685806355785</v>
+      </c>
+      <c r="C66">
+        <v>-2.508001886996646</v>
+      </c>
+      <c r="D66">
+        <v>1.632798113003354</v>
+      </c>
+      <c r="E66">
+        <v>0.4907999999999997</v>
+      </c>
+      <c r="F66">
+        <v>4.1408</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>2.82</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.107</v>
+      </c>
+      <c r="K66">
+        <v>0.094</v>
+      </c>
+      <c r="L66">
+        <v>0.013</v>
+      </c>
+      <c r="M66">
+        <v>0.98882304</v>
+      </c>
+      <c r="N66">
+        <v>-0.97582304</v>
+      </c>
+      <c r="O66">
+        <v>-0.1854063775999999</v>
+      </c>
+      <c r="P66">
+        <v>-0.7904166624</v>
+      </c>
+      <c r="Q66">
+        <v>-0.6964166624</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1436620628165005</v>
+      </c>
+      <c r="T66">
+        <v>1.421893348697629</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.002497919142337135</v>
+      </c>
+      <c r="W66">
+        <v>0.2382034969088099</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.01314694285440599</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2061685806355785</v>
+      </c>
+      <c r="C67">
+        <v>-2.592213292384717</v>
+      </c>
+      <c r="D67">
+        <v>1.613286707615283</v>
+      </c>
+      <c r="E67">
+        <v>0.5554999999999999</v>
+      </c>
+      <c r="F67">
+        <v>4.2055</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>2.82</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.107</v>
+      </c>
+      <c r="K67">
+        <v>0.094</v>
+      </c>
+      <c r="L67">
+        <v>0.013</v>
+      </c>
+      <c r="M67">
+        <v>1.0042734</v>
+      </c>
+      <c r="N67">
+        <v>-0.9912734</v>
+      </c>
+      <c r="O67">
+        <v>-0.188341946</v>
+      </c>
+      <c r="P67">
+        <v>-0.802931454</v>
+      </c>
+      <c r="Q67">
+        <v>-0.708931454</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1466581217541147</v>
+      </c>
+      <c r="T67">
+        <v>1.462518872946132</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.00245948961707041</v>
+      </c>
+      <c r="W67">
+        <v>0.2382126738794436</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.01294468219510747</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2081685806355785</v>
+      </c>
+      <c r="C68">
+        <v>-2.675963894350692</v>
+      </c>
+      <c r="D68">
+        <v>1.594236105649308</v>
+      </c>
+      <c r="E68">
+        <v>0.6202000000000001</v>
+      </c>
+      <c r="F68">
+        <v>4.2702</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>2.82</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.107</v>
+      </c>
+      <c r="K68">
+        <v>0.094</v>
+      </c>
+      <c r="L68">
+        <v>0.013</v>
+      </c>
+      <c r="M68">
+        <v>1.01972376</v>
+      </c>
+      <c r="N68">
+        <v>-1.00672376</v>
+      </c>
+      <c r="O68">
+        <v>-0.1912775144</v>
+      </c>
+      <c r="P68">
+        <v>-0.8154462456000001</v>
+      </c>
+      <c r="Q68">
+        <v>-0.7214462456000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1498304194527652</v>
+      </c>
+      <c r="T68">
+        <v>1.505534133915136</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.002422224622872374</v>
+      </c>
+      <c r="W68">
+        <v>0.2382215727600581</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.01274855064669667</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2101685806355785</v>
+      </c>
+      <c r="C69">
+        <v>-2.759269826660297</v>
+      </c>
+      <c r="D69">
+        <v>1.575630173339703</v>
+      </c>
+      <c r="E69">
+        <v>0.6849000000000003</v>
+      </c>
+      <c r="F69">
+        <v>4.3349</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>2.82</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.107</v>
+      </c>
+      <c r="K69">
+        <v>0.094</v>
+      </c>
+      <c r="L69">
+        <v>0.013</v>
+      </c>
+      <c r="M69">
+        <v>1.03517412</v>
+      </c>
+      <c r="N69">
+        <v>-1.02217412</v>
+      </c>
+      <c r="O69">
+        <v>-0.1942130828</v>
+      </c>
+      <c r="P69">
+        <v>-0.8279610372000004</v>
+      </c>
+      <c r="Q69">
+        <v>-0.7339610372000004</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1531949776180005</v>
+      </c>
+      <c r="T69">
+        <v>1.551156380397413</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.002386072016560846</v>
+      </c>
+      <c r="W69">
+        <v>0.2382302060024453</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.01255827377137275</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2121685806355785</v>
+      </c>
+      <c r="C70">
+        <v>-2.842146478595305</v>
+      </c>
+      <c r="D70">
+        <v>1.557453521404695</v>
+      </c>
+      <c r="E70">
+        <v>0.7496000000000005</v>
+      </c>
+      <c r="F70">
+        <v>4.3996</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>2.82</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.107</v>
+      </c>
+      <c r="K70">
+        <v>0.094</v>
+      </c>
+      <c r="L70">
+        <v>0.013</v>
+      </c>
+      <c r="M70">
+        <v>1.05062448</v>
+      </c>
+      <c r="N70">
+        <v>-1.03762448</v>
+      </c>
+      <c r="O70">
+        <v>-0.1971486512</v>
+      </c>
+      <c r="P70">
+        <v>-0.8404758288000003</v>
+      </c>
+      <c r="Q70">
+        <v>-0.7464758288000003</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.156769820668563</v>
+      </c>
+      <c r="T70">
+        <v>1.599630017284832</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.002350982722199657</v>
+      </c>
+      <c r="W70">
+        <v>0.2382385853259387</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.01237359327473497</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2141685806355785</v>
+      </c>
+      <c r="C71">
+        <v>-2.92460853740607</v>
+      </c>
+      <c r="D71">
+        <v>1.539691462593931</v>
+      </c>
+      <c r="E71">
+        <v>0.8143000000000007</v>
+      </c>
+      <c r="F71">
+        <v>4.464300000000001</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>2.82</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.107</v>
+      </c>
+      <c r="K71">
+        <v>0.094</v>
+      </c>
+      <c r="L71">
+        <v>0.013</v>
+      </c>
+      <c r="M71">
+        <v>1.06607484</v>
+      </c>
+      <c r="N71">
+        <v>-1.05307484</v>
+      </c>
+      <c r="O71">
+        <v>-0.2000842196</v>
+      </c>
+      <c r="P71">
+        <v>-0.8529906204000003</v>
+      </c>
+      <c r="Q71">
+        <v>-0.7589906204000003</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1605752987546457</v>
+      </c>
+      <c r="T71">
+        <v>1.651230985584343</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.002316910508834444</v>
+      </c>
+      <c r="W71">
+        <v>0.2382467217704904</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.01219426583597072</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2161685806355785</v>
+      </c>
+      <c r="C72">
+        <v>-3.006670027891889</v>
+      </c>
+      <c r="D72">
+        <v>1.522329972108111</v>
+      </c>
+      <c r="E72">
+        <v>0.879</v>
+      </c>
+      <c r="F72">
+        <v>4.529</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>2.82</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.107</v>
+      </c>
+      <c r="K72">
+        <v>0.094</v>
+      </c>
+      <c r="L72">
+        <v>0.013</v>
+      </c>
+      <c r="M72">
+        <v>1.0815252</v>
+      </c>
+      <c r="N72">
+        <v>-1.0685252</v>
+      </c>
+      <c r="O72">
+        <v>-0.203019788</v>
+      </c>
+      <c r="P72">
+        <v>-0.8655054120000001</v>
+      </c>
+      <c r="Q72">
+        <v>-0.7715054120000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1646344753798006</v>
+      </c>
+      <c r="T72">
+        <v>1.706272018437155</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.002283811787279667</v>
+      </c>
+      <c r="W72">
+        <v>0.2382546257451976</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.01202006203831396</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2181685806355785</v>
+      </c>
+      <c r="C73">
+        <v>-3.0883443493334</v>
+      </c>
+      <c r="D73">
+        <v>1.505355650666599</v>
+      </c>
+      <c r="E73">
+        <v>0.9436999999999993</v>
+      </c>
+      <c r="F73">
+        <v>4.593699999999999</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>2.82</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.107</v>
+      </c>
+      <c r="K73">
+        <v>0.094</v>
+      </c>
+      <c r="L73">
+        <v>0.013</v>
+      </c>
+      <c r="M73">
+        <v>1.09697556</v>
+      </c>
+      <c r="N73">
+        <v>-1.08397556</v>
+      </c>
+      <c r="O73">
+        <v>-0.2059553564</v>
+      </c>
+      <c r="P73">
+        <v>-0.8780202036000001</v>
+      </c>
+      <c r="Q73">
+        <v>-0.7840202036000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1689735952204833</v>
+      </c>
+      <c r="T73">
+        <v>1.765108984590159</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.002251645424078544</v>
+      </c>
+      <c r="W73">
+        <v>0.2382623070727301</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.01185076538988694</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2201685806355785</v>
+      </c>
+      <c r="C74">
+        <v>-3.169644309981395</v>
+      </c>
+      <c r="D74">
+        <v>1.488755690018605</v>
+      </c>
+      <c r="E74">
+        <v>1.0084</v>
+      </c>
+      <c r="F74">
+        <v>4.658399999999999</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>2.82</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.107</v>
+      </c>
+      <c r="K74">
+        <v>0.094</v>
+      </c>
+      <c r="L74">
+        <v>0.013</v>
+      </c>
+      <c r="M74">
+        <v>1.11242592</v>
+      </c>
+      <c r="N74">
+        <v>-1.09942592</v>
+      </c>
+      <c r="O74">
+        <v>-0.2088909248</v>
+      </c>
+      <c r="P74">
+        <v>-0.8905349952000001</v>
+      </c>
+      <c r="Q74">
+        <v>-0.7965349952000002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1736226521926434</v>
+      </c>
+      <c r="T74">
+        <v>1.828148591182665</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.002220372570966343</v>
+      </c>
+      <c r="W74">
+        <v>0.2382697750300533</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.01168617142613859</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2221685806355785</v>
+      </c>
+      <c r="C75">
+        <v>-3.250582159288604</v>
+      </c>
+      <c r="D75">
+        <v>1.472517840711396</v>
+      </c>
+      <c r="E75">
+        <v>1.0731</v>
+      </c>
+      <c r="F75">
+        <v>4.7231</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>2.82</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.107</v>
+      </c>
+      <c r="K75">
+        <v>0.094</v>
+      </c>
+      <c r="L75">
+        <v>0.013</v>
+      </c>
+      <c r="M75">
+        <v>1.12787628</v>
+      </c>
+      <c r="N75">
+        <v>-1.11487628</v>
+      </c>
+      <c r="O75">
+        <v>-0.2118264931999999</v>
+      </c>
+      <c r="P75">
+        <v>-0.9030497868000001</v>
+      </c>
+      <c r="Q75">
+        <v>-0.8090497868000002</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1786160837553339</v>
+      </c>
+      <c r="T75">
+        <v>1.895857798263504</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.002189956508350365</v>
+      </c>
+      <c r="W75">
+        <v>0.2382770383858059</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.0115260868860545</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2241685806355785</v>
+      </c>
+      <c r="C76">
+        <v>-3.331169618054944</v>
+      </c>
+      <c r="D76">
+        <v>1.456630381945055</v>
+      </c>
+      <c r="E76">
+        <v>1.1378</v>
+      </c>
+      <c r="F76">
+        <v>4.7878</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>2.82</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.107</v>
+      </c>
+      <c r="K76">
+        <v>0.094</v>
+      </c>
+      <c r="L76">
+        <v>0.013</v>
+      </c>
+      <c r="M76">
+        <v>1.14332664</v>
+      </c>
+      <c r="N76">
+        <v>-1.13032664</v>
+      </c>
+      <c r="O76">
+        <v>-0.2147620615999999</v>
+      </c>
+      <c r="P76">
+        <v>-0.9155645784000002</v>
+      </c>
+      <c r="Q76">
+        <v>-0.8215645784000002</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1839936254382314</v>
+      </c>
+      <c r="T76">
+        <v>1.968775405889024</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.002160362501480766</v>
+      </c>
+      <c r="W76">
+        <v>0.2382841054346464</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.01137032895516188</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2261685806355785</v>
+      </c>
+      <c r="C77">
+        <v>-3.411417906642113</v>
+      </c>
+      <c r="D77">
+        <v>1.441082093357887</v>
+      </c>
+      <c r="E77">
+        <v>1.2025</v>
+      </c>
+      <c r="F77">
+        <v>4.8525</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>2.82</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.107</v>
+      </c>
+      <c r="K77">
+        <v>0.094</v>
+      </c>
+      <c r="L77">
+        <v>0.013</v>
+      </c>
+      <c r="M77">
+        <v>1.158777</v>
+      </c>
+      <c r="N77">
+        <v>-1.145777</v>
+      </c>
+      <c r="O77">
+        <v>-0.21769763</v>
+      </c>
+      <c r="P77">
+        <v>-0.9280793700000003</v>
+      </c>
+      <c r="Q77">
+        <v>-0.8340793700000003</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1898013704557606</v>
+      </c>
+      <c r="T77">
+        <v>2.047526422124585</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.002131557668127688</v>
+      </c>
+      <c r="W77">
+        <v>0.2382909840288511</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.01121872456909301</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2281685806355785</v>
+      </c>
+      <c r="C78">
+        <v>-3.491337771400261</v>
+      </c>
+      <c r="D78">
+        <v>1.42586222859974</v>
+      </c>
+      <c r="E78">
+        <v>1.2672</v>
+      </c>
+      <c r="F78">
+        <v>4.9172</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>2.82</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.107</v>
+      </c>
+      <c r="K78">
+        <v>0.094</v>
+      </c>
+      <c r="L78">
+        <v>0.013</v>
+      </c>
+      <c r="M78">
+        <v>1.17422736</v>
+      </c>
+      <c r="N78">
+        <v>-1.16122736</v>
+      </c>
+      <c r="O78">
+        <v>-0.2206331984</v>
+      </c>
+      <c r="P78">
+        <v>-0.9405941616000003</v>
+      </c>
+      <c r="Q78">
+        <v>-0.8465941616000003</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1960930942247507</v>
+      </c>
+      <c r="T78">
+        <v>2.132840023046443</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.002103510856704956</v>
+      </c>
+      <c r="W78">
+        <v>0.2382976816074189</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.01107110977213122</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2301685806355785</v>
+      </c>
+      <c r="C79">
+        <v>-3.57093950943755</v>
+      </c>
+      <c r="D79">
+        <v>1.41096049056245</v>
+      </c>
+      <c r="E79">
+        <v>1.3319</v>
+      </c>
+      <c r="F79">
+        <v>4.9819</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>2.82</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.107</v>
+      </c>
+      <c r="K79">
+        <v>0.094</v>
+      </c>
+      <c r="L79">
+        <v>0.013</v>
+      </c>
+      <c r="M79">
+        <v>1.18967772</v>
+      </c>
+      <c r="N79">
+        <v>-1.17667772</v>
+      </c>
+      <c r="O79">
+        <v>-0.2235687668</v>
+      </c>
+      <c r="P79">
+        <v>-0.9531089532000001</v>
+      </c>
+      <c r="Q79">
+        <v>-0.8591089532000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2029319244084355</v>
+      </c>
+      <c r="T79">
+        <v>2.225572197961506</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.002076192533890606</v>
+      </c>
+      <c r="W79">
+        <v>0.2383042052229069</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.0109273291257399</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2321685806355785</v>
+      </c>
+      <c r="C80">
+        <v>-3.650232991852581</v>
+      </c>
+      <c r="D80">
+        <v>1.396367008147418</v>
+      </c>
+      <c r="E80">
+        <v>1.3966</v>
+      </c>
+      <c r="F80">
+        <v>5.0466</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>2.82</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.107</v>
+      </c>
+      <c r="K80">
+        <v>0.094</v>
+      </c>
+      <c r="L80">
+        <v>0.013</v>
+      </c>
+      <c r="M80">
+        <v>1.20512808</v>
+      </c>
+      <c r="N80">
+        <v>-1.19212808</v>
+      </c>
+      <c r="O80">
+        <v>-0.2265043351999999</v>
+      </c>
+      <c r="P80">
+        <v>-0.9656237448000001</v>
+      </c>
+      <c r="Q80">
+        <v>-0.8716237448000002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2103924664270007</v>
+      </c>
+      <c r="T80">
+        <v>2.326734570596119</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.002049574680892009</v>
+      </c>
+      <c r="W80">
+        <v>0.238310561566203</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.01078723516258939</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2341685806355785</v>
+      </c>
+      <c r="C81">
+        <v>-3.729227685539813</v>
+      </c>
+      <c r="D81">
+        <v>1.382072314460187</v>
+      </c>
+      <c r="E81">
+        <v>1.4613</v>
+      </c>
+      <c r="F81">
+        <v>5.1113</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>2.82</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.107</v>
+      </c>
+      <c r="K81">
+        <v>0.094</v>
+      </c>
+      <c r="L81">
+        <v>0.013</v>
+      </c>
+      <c r="M81">
+        <v>1.22057844</v>
+      </c>
+      <c r="N81">
+        <v>-1.20757844</v>
+      </c>
+      <c r="O81">
+        <v>-0.2294399036</v>
+      </c>
+      <c r="P81">
+        <v>-0.9781385364000003</v>
+      </c>
+      <c r="Q81">
+        <v>-0.8841385364000003</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2185635362568579</v>
+      </c>
+      <c r="T81">
+        <v>2.437531454910221</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.002023630697589578</v>
+      </c>
+      <c r="W81">
+        <v>0.2383167569894156</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.01065068788205037</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2361685806355785</v>
+      </c>
+      <c r="C82">
+        <v>-3.807932673669226</v>
+      </c>
+      <c r="D82">
+        <v>1.368067326330774</v>
+      </c>
+      <c r="E82">
+        <v>1.526</v>
+      </c>
+      <c r="F82">
+        <v>5.176</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>2.82</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.107</v>
+      </c>
+      <c r="K82">
+        <v>0.094</v>
+      </c>
+      <c r="L82">
+        <v>0.013</v>
+      </c>
+      <c r="M82">
+        <v>1.2360288</v>
+      </c>
+      <c r="N82">
+        <v>-1.2230288</v>
+      </c>
+      <c r="O82">
+        <v>-0.232375472</v>
+      </c>
+      <c r="P82">
+        <v>-0.9906533280000003</v>
+      </c>
+      <c r="Q82">
+        <v>-0.8966533280000003</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2275517130697008</v>
+      </c>
+      <c r="T82">
+        <v>2.559408027655732</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.001998335313869708</v>
+      </c>
+      <c r="W82">
+        <v>0.2383227975270479</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.01051755428352474</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2381685806355785</v>
+      </c>
+      <c r="C83">
+        <v>-3.886356674933312</v>
+      </c>
+      <c r="D83">
+        <v>1.354343325066688</v>
+      </c>
+      <c r="E83">
+        <v>1.5907</v>
+      </c>
+      <c r="F83">
+        <v>5.2407</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>2.82</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.107</v>
+      </c>
+      <c r="K83">
+        <v>0.094</v>
+      </c>
+      <c r="L83">
+        <v>0.013</v>
+      </c>
+      <c r="M83">
+        <v>1.25147916</v>
+      </c>
+      <c r="N83">
+        <v>-1.23847916</v>
+      </c>
+      <c r="O83">
+        <v>-0.2353110404</v>
+      </c>
+      <c r="P83">
+        <v>-1.0031681196</v>
+      </c>
+      <c r="Q83">
+        <v>-0.9091681196000002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2374860137575798</v>
+      </c>
+      <c r="T83">
+        <v>2.694113713321823</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.001973664507525637</v>
+      </c>
+      <c r="W83">
+        <v>0.2383286889156029</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.0103877079343454</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2401685806355785</v>
+      </c>
+      <c r="C84">
+        <v>-3.964508061647089</v>
+      </c>
+      <c r="D84">
+        <v>1.340891938352912</v>
+      </c>
+      <c r="E84">
+        <v>1.655400000000001</v>
+      </c>
+      <c r="F84">
+        <v>5.305400000000001</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>2.82</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.107</v>
+      </c>
+      <c r="K84">
+        <v>0.094</v>
+      </c>
+      <c r="L84">
+        <v>0.013</v>
+      </c>
+      <c r="M84">
+        <v>1.26692952</v>
+      </c>
+      <c r="N84">
+        <v>-1.25392952</v>
+      </c>
+      <c r="O84">
+        <v>-0.2382466088</v>
+      </c>
+      <c r="P84">
+        <v>-1.0156829112</v>
+      </c>
+      <c r="Q84">
+        <v>-0.9216829112000003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2485241256330009</v>
+      </c>
+      <c r="T84">
+        <v>2.843786697395258</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.001949595428165569</v>
+      </c>
+      <c r="W84">
+        <v>0.2383344366117541</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.01026102856929234</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2421685806355785</v>
+      </c>
+      <c r="C85">
+        <v>-4.042394876780107</v>
+      </c>
+      <c r="D85">
+        <v>1.327705123219893</v>
+      </c>
+      <c r="E85">
+        <v>1.7201</v>
+      </c>
+      <c r="F85">
+        <v>5.3701</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>2.82</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.107</v>
+      </c>
+      <c r="K85">
+        <v>0.094</v>
+      </c>
+      <c r="L85">
+        <v>0.013</v>
+      </c>
+      <c r="M85">
+        <v>1.28237988</v>
+      </c>
+      <c r="N85">
+        <v>-1.26937988</v>
+      </c>
+      <c r="O85">
+        <v>-0.2411821772</v>
+      </c>
+      <c r="P85">
+        <v>-1.0281977028</v>
+      </c>
+      <c r="Q85">
+        <v>-0.9341977028000003</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2608608389055305</v>
+      </c>
+      <c r="T85">
+        <v>3.011068267830273</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.001926106326621405</v>
+      </c>
+      <c r="W85">
+        <v>0.2383400458092028</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.01013740171905997</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2441685806355785</v>
+      </c>
+      <c r="C86">
+        <v>-4.120024849993252</v>
+      </c>
+      <c r="D86">
+        <v>1.314775150006747</v>
+      </c>
+      <c r="E86">
+        <v>1.784799999999999</v>
+      </c>
+      <c r="F86">
+        <v>5.434799999999999</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>2.82</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.107</v>
+      </c>
+      <c r="K86">
+        <v>0.094</v>
+      </c>
+      <c r="L86">
+        <v>0.013</v>
+      </c>
+      <c r="M86">
+        <v>1.29783024</v>
+      </c>
+      <c r="N86">
+        <v>-1.28483024</v>
+      </c>
+      <c r="O86">
+        <v>-0.2441177455999999</v>
+      </c>
+      <c r="P86">
+        <v>-1.0407124944</v>
+      </c>
+      <c r="Q86">
+        <v>-0.9467124944000002</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2747396413371259</v>
+      </c>
+      <c r="T86">
+        <v>3.199260034569664</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.001903176489399722</v>
+      </c>
+      <c r="W86">
+        <v>0.2383455214543314</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.01001671836526163</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2461685806355785</v>
+      </c>
+      <c r="C87">
+        <v>-4.197405412747523</v>
+      </c>
+      <c r="D87">
+        <v>1.302094587252477</v>
+      </c>
+      <c r="E87">
+        <v>1.849499999999999</v>
+      </c>
+      <c r="F87">
+        <v>5.499499999999999</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>2.82</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.107</v>
+      </c>
+      <c r="K87">
+        <v>0.094</v>
+      </c>
+      <c r="L87">
+        <v>0.013</v>
+      </c>
+      <c r="M87">
+        <v>1.3132806</v>
+      </c>
+      <c r="N87">
+        <v>-1.3002806</v>
+      </c>
+      <c r="O87">
+        <v>-0.2470533139999999</v>
+      </c>
+      <c r="P87">
+        <v>-1.053227286</v>
+      </c>
+      <c r="Q87">
+        <v>-0.9592272860000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.290468950759601</v>
+      </c>
+      <c r="T87">
+        <v>3.412544036874308</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.001880786177759726</v>
+      </c>
+      <c r="W87">
+        <v>0.238350868260751</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.009898874619788001</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2481685806355785</v>
+      </c>
+      <c r="C88">
+        <v>-4.27454371254685</v>
+      </c>
+      <c r="D88">
+        <v>1.28965628745315</v>
+      </c>
+      <c r="E88">
+        <v>1.9142</v>
+      </c>
+      <c r="F88">
+        <v>5.5642</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>2.82</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.107</v>
+      </c>
+      <c r="K88">
+        <v>0.094</v>
+      </c>
+      <c r="L88">
+        <v>0.013</v>
+      </c>
+      <c r="M88">
+        <v>1.32873096</v>
+      </c>
+      <c r="N88">
+        <v>-1.31573096</v>
+      </c>
+      <c r="O88">
+        <v>-0.2499888823999999</v>
+      </c>
+      <c r="P88">
+        <v>-1.0657420776</v>
+      </c>
+      <c r="Q88">
+        <v>-0.9717420776000002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3084453043852868</v>
+      </c>
+      <c r="T88">
+        <v>3.65629718236533</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.001858916571041589</v>
+      </c>
+      <c r="W88">
+        <v>0.2383560907228353</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.009783771426534638</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2501685806355785</v>
+      </c>
+      <c r="C89">
+        <v>-4.351446626372313</v>
+      </c>
+      <c r="D89">
+        <v>1.277453373627687</v>
+      </c>
+      <c r="E89">
+        <v>1.9789</v>
+      </c>
+      <c r="F89">
+        <v>5.6289</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>2.82</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.107</v>
+      </c>
+      <c r="K89">
+        <v>0.094</v>
+      </c>
+      <c r="L89">
+        <v>0.013</v>
+      </c>
+      <c r="M89">
+        <v>1.34418132</v>
+      </c>
+      <c r="N89">
+        <v>-1.33118132</v>
+      </c>
+      <c r="O89">
+        <v>-0.2529244508</v>
+      </c>
+      <c r="P89">
+        <v>-1.0782568692</v>
+      </c>
+      <c r="Q89">
+        <v>-0.9842568692000003</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3291872508764627</v>
+      </c>
+      <c r="T89">
+        <v>3.937550811778048</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.00183754971390318</v>
+      </c>
+      <c r="W89">
+        <v>0.2383611931283199</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.009671314283700827</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2521685806355785</v>
+      </c>
+      <c r="C90">
+        <v>-4.428120773360801</v>
+      </c>
+      <c r="D90">
+        <v>1.265479226639199</v>
+      </c>
+      <c r="E90">
+        <v>2.0436</v>
+      </c>
+      <c r="F90">
+        <v>5.6936</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>2.82</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.107</v>
+      </c>
+      <c r="K90">
+        <v>0.094</v>
+      </c>
+      <c r="L90">
+        <v>0.013</v>
+      </c>
+      <c r="M90">
+        <v>1.35963168</v>
+      </c>
+      <c r="N90">
+        <v>-1.34663168</v>
+      </c>
+      <c r="O90">
+        <v>-0.2558600192</v>
+      </c>
+      <c r="P90">
+        <v>-1.0907716608</v>
+      </c>
+      <c r="Q90">
+        <v>-0.9967716608000002</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3533861884495013</v>
+      </c>
+      <c r="T90">
+        <v>4.265680046092886</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.00181666846715428</v>
+      </c>
+      <c r="W90">
+        <v>0.2383661795700436</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.009561412985022444</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2541685806355785</v>
+      </c>
+      <c r="C91">
+        <v>-4.504572526777243</v>
+      </c>
+      <c r="D91">
+        <v>1.253727473222757</v>
+      </c>
+      <c r="E91">
+        <v>2.1083</v>
+      </c>
+      <c r="F91">
+        <v>5.7583</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>2.82</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.107</v>
+      </c>
+      <c r="K91">
+        <v>0.094</v>
+      </c>
+      <c r="L91">
+        <v>0.013</v>
+      </c>
+      <c r="M91">
+        <v>1.37508204</v>
+      </c>
+      <c r="N91">
+        <v>-1.36208204</v>
+      </c>
+      <c r="O91">
+        <v>-0.2587955876</v>
+      </c>
+      <c r="P91">
+        <v>-1.1032864524</v>
+      </c>
+      <c r="Q91">
+        <v>-1.0092864524</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3819849328540014</v>
+      </c>
+      <c r="T91">
+        <v>4.653469141192239</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.001796256461905356</v>
+      </c>
+      <c r="W91">
+        <v>0.238371053956897</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.009453981378449217</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2561685806355785</v>
+      </c>
+      <c r="C92">
+        <v>-4.5808080253259</v>
+      </c>
+      <c r="D92">
+        <v>1.242191974674099</v>
+      </c>
+      <c r="E92">
+        <v>2.173</v>
+      </c>
+      <c r="F92">
+        <v>5.823</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>2.82</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.107</v>
+      </c>
+      <c r="K92">
+        <v>0.094</v>
+      </c>
+      <c r="L92">
+        <v>0.013</v>
+      </c>
+      <c r="M92">
+        <v>1.3905324</v>
+      </c>
+      <c r="N92">
+        <v>-1.3775324</v>
+      </c>
+      <c r="O92">
+        <v>-0.2617311559999999</v>
+      </c>
+      <c r="P92">
+        <v>-1.115801244</v>
+      </c>
+      <c r="Q92">
+        <v>-1.021801244</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4163034261394016</v>
+      </c>
+      <c r="T92">
+        <v>5.118816055311464</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.001776298056773074</v>
+      </c>
+      <c r="W92">
+        <v>0.2383758200240426</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.009348937140910896</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2581685806355785</v>
+      </c>
+      <c r="C93">
+        <v>-4.656833183842904</v>
+      </c>
+      <c r="D93">
+        <v>1.230866816157095</v>
+      </c>
+      <c r="E93">
+        <v>2.2377</v>
+      </c>
+      <c r="F93">
+        <v>5.8877</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>2.82</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.107</v>
+      </c>
+      <c r="K93">
+        <v>0.094</v>
+      </c>
+      <c r="L93">
+        <v>0.013</v>
+      </c>
+      <c r="M93">
+        <v>1.40598276</v>
+      </c>
+      <c r="N93">
+        <v>-1.39298276</v>
+      </c>
+      <c r="O93">
+        <v>-0.2646667243999999</v>
+      </c>
+      <c r="P93">
+        <v>-1.1283160356</v>
+      </c>
+      <c r="Q93">
+        <v>-1.0343160356</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4582482512660018</v>
+      </c>
+      <c r="T93">
+        <v>5.687573394790515</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.001756778297907436</v>
+      </c>
+      <c r="W93">
+        <v>0.2383804813424597</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.009246201567933765</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2601685806355785</v>
+      </c>
+      <c r="C94">
+        <v>-4.732653703409169</v>
+      </c>
+      <c r="D94">
+        <v>1.219746296590831</v>
+      </c>
+      <c r="E94">
+        <v>2.3024</v>
+      </c>
+      <c r="F94">
+        <v>5.9524</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>2.82</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.107</v>
+      </c>
+      <c r="K94">
+        <v>0.094</v>
+      </c>
+      <c r="L94">
+        <v>0.013</v>
+      </c>
+      <c r="M94">
+        <v>1.42143312</v>
+      </c>
+      <c r="N94">
+        <v>-1.40843312</v>
+      </c>
+      <c r="O94">
+        <v>-0.2676022928</v>
+      </c>
+      <c r="P94">
+        <v>-1.1408308272</v>
+      </c>
+      <c r="Q94">
+        <v>-1.0468308272</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5106792826742522</v>
+      </c>
+      <c r="T94">
+        <v>6.398520069139332</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.001737682881625833</v>
+      </c>
+      <c r="W94">
+        <v>0.2383850413278678</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.009145699376977956</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2621685806355785</v>
+      </c>
+      <c r="C95">
+        <v>-4.808275080920009</v>
+      </c>
+      <c r="D95">
+        <v>1.208824919079991</v>
+      </c>
+      <c r="E95">
+        <v>2.3671</v>
+      </c>
+      <c r="F95">
+        <v>6.0171</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>2.82</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.107</v>
+      </c>
+      <c r="K95">
+        <v>0.094</v>
+      </c>
+      <c r="L95">
+        <v>0.013</v>
+      </c>
+      <c r="M95">
+        <v>1.43688348</v>
+      </c>
+      <c r="N95">
+        <v>-1.42388348</v>
+      </c>
+      <c r="O95">
+        <v>-0.2705378612</v>
+      </c>
+      <c r="P95">
+        <v>-1.1533456188</v>
+      </c>
+      <c r="Q95">
+        <v>-1.0593456188</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5780906087705739</v>
+      </c>
+      <c r="T95">
+        <v>7.312594364730665</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.001718998119457813</v>
+      </c>
+      <c r="W95">
+        <v>0.2383895032490735</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.009047358523462057</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2641685806355785</v>
+      </c>
+      <c r="C96">
+        <v>-4.883702618145215</v>
+      </c>
+      <c r="D96">
+        <v>1.198097381854785</v>
+      </c>
+      <c r="E96">
+        <v>2.4318</v>
+      </c>
+      <c r="F96">
+        <v>6.0818</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>2.82</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.107</v>
+      </c>
+      <c r="K96">
+        <v>0.094</v>
+      </c>
+      <c r="L96">
+        <v>0.013</v>
+      </c>
+      <c r="M96">
+        <v>1.45233384</v>
+      </c>
+      <c r="N96">
+        <v>-1.43933384</v>
+      </c>
+      <c r="O96">
+        <v>-0.2734734296</v>
+      </c>
+      <c r="P96">
+        <v>-1.1658604104</v>
+      </c>
+      <c r="Q96">
+        <v>-1.0718604104</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.6679723768990031</v>
+      </c>
+      <c r="T96">
+        <v>8.531360092185778</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.001700710905421028</v>
+      </c>
+      <c r="W96">
+        <v>0.2383938702357855</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.008951110028531661</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2661685806355785</v>
+      </c>
+      <c r="C97">
+        <v>-4.958941430310958</v>
+      </c>
+      <c r="D97">
+        <v>1.187558569689043</v>
+      </c>
+      <c r="E97">
+        <v>2.496500000000001</v>
+      </c>
+      <c r="F97">
+        <v>6.146500000000001</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>2.82</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.107</v>
+      </c>
+      <c r="K97">
+        <v>0.094</v>
+      </c>
+      <c r="L97">
+        <v>0.013</v>
+      </c>
+      <c r="M97">
+        <v>1.4677842</v>
+      </c>
+      <c r="N97">
+        <v>-1.4547842</v>
+      </c>
+      <c r="O97">
+        <v>-0.276408998</v>
+      </c>
+      <c r="P97">
+        <v>-1.178375202</v>
+      </c>
+      <c r="Q97">
+        <v>-1.084375202</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.7938068522788042</v>
+      </c>
+      <c r="T97">
+        <v>10.23763211062294</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.001682808685363965</v>
+      </c>
+      <c r="W97">
+        <v>0.2383981452859351</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.008856887817704995</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2681685806355785</v>
+      </c>
+      <c r="C98">
+        <v>-5.033996454232701</v>
+      </c>
+      <c r="D98">
+        <v>1.177203545767299</v>
+      </c>
+      <c r="E98">
+        <v>2.5612</v>
+      </c>
+      <c r="F98">
+        <v>6.2112</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>2.82</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.107</v>
+      </c>
+      <c r="K98">
+        <v>0.094</v>
+      </c>
+      <c r="L98">
+        <v>0.013</v>
+      </c>
+      <c r="M98">
+        <v>1.48323456</v>
+      </c>
+      <c r="N98">
+        <v>-1.47023456</v>
+      </c>
+      <c r="O98">
+        <v>-0.2793445663999999</v>
+      </c>
+      <c r="P98">
+        <v>-1.1908899936</v>
+      </c>
+      <c r="Q98">
+        <v>-1.0968899936</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.9825585653485032</v>
+      </c>
+      <c r="T98">
+        <v>12.79704013827865</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.001665279428224757</v>
+      </c>
+      <c r="W98">
+        <v>0.2384023312725399</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.008764628569603916</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2701685806355785</v>
+      </c>
+      <c r="C99">
+        <v>-5.108872456026319</v>
+      </c>
+      <c r="D99">
+        <v>1.16702754397368</v>
+      </c>
+      <c r="E99">
+        <v>2.625899999999999</v>
+      </c>
+      <c r="F99">
+        <v>6.275899999999999</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>2.82</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.107</v>
+      </c>
+      <c r="K99">
+        <v>0.094</v>
+      </c>
+      <c r="L99">
+        <v>0.013</v>
+      </c>
+      <c r="M99">
+        <v>1.49868492</v>
+      </c>
+      <c r="N99">
+        <v>-1.48568492</v>
+      </c>
+      <c r="O99">
+        <v>-0.2822801347999999</v>
+      </c>
+      <c r="P99">
+        <v>-1.2034047852</v>
+      </c>
+      <c r="Q99">
+        <v>-1.1094047852</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.297144753798004</v>
+      </c>
+      <c r="T99">
+        <v>17.06272018437153</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.001648111599067801</v>
+      </c>
+      <c r="W99">
+        <v>0.2384064309501426</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.008674271574040993</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2721685806355785</v>
+      </c>
+      <c r="C100">
+        <v>-5.183574038422675</v>
+      </c>
+      <c r="D100">
+        <v>1.157025961577325</v>
+      </c>
+      <c r="E100">
+        <v>2.690599999999999</v>
+      </c>
+      <c r="F100">
+        <v>6.340599999999999</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>2.82</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.107</v>
+      </c>
+      <c r="K100">
+        <v>0.094</v>
+      </c>
+      <c r="L100">
+        <v>0.013</v>
+      </c>
+      <c r="M100">
+        <v>1.51413528</v>
+      </c>
+      <c r="N100">
+        <v>-1.50113528</v>
+      </c>
+      <c r="O100">
+        <v>-0.2852157031999999</v>
+      </c>
+      <c r="P100">
+        <v>-1.2159195768</v>
+      </c>
+      <c r="Q100">
+        <v>-1.1219195768</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.926317130697006</v>
+      </c>
+      <c r="T100">
+        <v>25.59408027655729</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.001631294133771191</v>
+      </c>
+      <c r="W100">
+        <v>0.2384104469608554</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.008585758598795623</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2741685806355785</v>
+      </c>
+      <c r="C101">
+        <v>-5.258105647709292</v>
+      </c>
+      <c r="D101">
+        <v>1.147194352290707</v>
+      </c>
+      <c r="E101">
+        <v>2.7553</v>
+      </c>
+      <c r="F101">
+        <v>6.4053</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>2.82</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.107</v>
+      </c>
+      <c r="K101">
+        <v>0.094</v>
+      </c>
+      <c r="L101">
+        <v>0.013</v>
+      </c>
+      <c r="M101">
+        <v>1.52958564</v>
+      </c>
+      <c r="N101">
+        <v>-1.51658564</v>
+      </c>
+      <c r="O101">
+        <v>-0.2881512716</v>
+      </c>
+      <c r="P101">
+        <v>-1.2284343684</v>
+      </c>
+      <c r="Q101">
+        <v>-1.1344343684</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.813834261394013</v>
+      </c>
+      <c r="T101">
+        <v>51.18816055311459</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.001614816415248249</v>
+      </c>
+      <c r="W101">
+        <v>0.2384143818400387</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.00849903376446437</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
